--- a/資料/ガントチャート_4GA3_遠藤直樹.xlsx
+++ b/資料/ガントチャート_4GA3_遠藤直樹.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7383AF-ACA2-47D9-9734-F13B4D5EA431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBC25EC-7050-4B43-991F-613559887970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="制作進捗確認表" sheetId="16" state="hidden" r:id="rId1"/>
@@ -37,6 +37,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1854,14 +1857,27 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="17" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1872,15 +1888,6 @@
     <xf numFmtId="183" fontId="23" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="17" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1889,10 +1896,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2491,15 +2494,15 @@
       <c r="G1" s="114"/>
     </row>
     <row r="2" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -2507,15 +2510,15 @@
       <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A3" s="115" t="s">
+      <c r="A3" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -2523,15 +2526,15 @@
       <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A4" s="115" t="s">
+      <c r="A4" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="115"/>
-      <c r="C4" s="115"/>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -2539,10 +2542,10 @@
       <c r="L4" s="83"/>
     </row>
     <row r="5" spans="1:92" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
       <c r="AU5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2555,161 +2558,161 @@
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="113">
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="115">
         <f>H7</f>
         <v>45761</v>
       </c>
-      <c r="I6" s="113"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="113"/>
-      <c r="L6" s="113"/>
-      <c r="M6" s="113">
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115">
         <f>H6+7</f>
         <v>45768</v>
       </c>
-      <c r="N6" s="113"/>
-      <c r="O6" s="113"/>
-      <c r="P6" s="113"/>
-      <c r="Q6" s="113"/>
-      <c r="R6" s="113">
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="115">
         <f>M6+7</f>
         <v>45775</v>
       </c>
-      <c r="S6" s="113"/>
-      <c r="T6" s="113"/>
-      <c r="U6" s="113"/>
-      <c r="V6" s="113"/>
-      <c r="W6" s="113">
+      <c r="S6" s="115"/>
+      <c r="T6" s="115"/>
+      <c r="U6" s="115"/>
+      <c r="V6" s="115"/>
+      <c r="W6" s="115">
         <f>R6+7</f>
         <v>45782</v>
       </c>
-      <c r="X6" s="113"/>
-      <c r="Y6" s="113"/>
-      <c r="Z6" s="113"/>
-      <c r="AA6" s="113"/>
-      <c r="AB6" s="113">
+      <c r="X6" s="115"/>
+      <c r="Y6" s="115"/>
+      <c r="Z6" s="115"/>
+      <c r="AA6" s="115"/>
+      <c r="AB6" s="115">
         <f>W6+7</f>
         <v>45789</v>
       </c>
-      <c r="AC6" s="113"/>
-      <c r="AD6" s="113"/>
-      <c r="AE6" s="113"/>
-      <c r="AF6" s="113"/>
-      <c r="AG6" s="113">
+      <c r="AC6" s="115"/>
+      <c r="AD6" s="115"/>
+      <c r="AE6" s="115"/>
+      <c r="AF6" s="115"/>
+      <c r="AG6" s="115">
         <f>AB6+7</f>
         <v>45796</v>
       </c>
-      <c r="AH6" s="113"/>
-      <c r="AI6" s="113"/>
-      <c r="AJ6" s="113"/>
-      <c r="AK6" s="113"/>
-      <c r="AL6" s="113">
+      <c r="AH6" s="115"/>
+      <c r="AI6" s="115"/>
+      <c r="AJ6" s="115"/>
+      <c r="AK6" s="115"/>
+      <c r="AL6" s="115">
         <f>AG6+7</f>
         <v>45803</v>
       </c>
-      <c r="AM6" s="113"/>
-      <c r="AN6" s="113"/>
-      <c r="AO6" s="113"/>
-      <c r="AP6" s="113"/>
-      <c r="AQ6" s="113">
+      <c r="AM6" s="115"/>
+      <c r="AN6" s="115"/>
+      <c r="AO6" s="115"/>
+      <c r="AP6" s="115"/>
+      <c r="AQ6" s="115">
         <f>AL6+7</f>
         <v>45810</v>
       </c>
-      <c r="AR6" s="113"/>
-      <c r="AS6" s="113"/>
-      <c r="AT6" s="113"/>
-      <c r="AU6" s="113"/>
-      <c r="AV6" s="113">
+      <c r="AR6" s="115"/>
+      <c r="AS6" s="115"/>
+      <c r="AT6" s="115"/>
+      <c r="AU6" s="115"/>
+      <c r="AV6" s="115">
         <f>AQ6+7</f>
         <v>45817</v>
       </c>
-      <c r="AW6" s="113"/>
-      <c r="AX6" s="113"/>
-      <c r="AY6" s="113"/>
-      <c r="AZ6" s="113"/>
-      <c r="BA6" s="113">
+      <c r="AW6" s="115"/>
+      <c r="AX6" s="115"/>
+      <c r="AY6" s="115"/>
+      <c r="AZ6" s="115"/>
+      <c r="BA6" s="115">
         <f>AV6+7</f>
         <v>45824</v>
       </c>
-      <c r="BB6" s="113"/>
-      <c r="BC6" s="113"/>
-      <c r="BD6" s="113"/>
-      <c r="BE6" s="113"/>
-      <c r="BF6" s="113">
+      <c r="BB6" s="115"/>
+      <c r="BC6" s="115"/>
+      <c r="BD6" s="115"/>
+      <c r="BE6" s="115"/>
+      <c r="BF6" s="115">
         <f>BA6+7</f>
         <v>45831</v>
       </c>
-      <c r="BG6" s="113"/>
-      <c r="BH6" s="113"/>
-      <c r="BI6" s="113"/>
-      <c r="BJ6" s="113"/>
-      <c r="BK6" s="113">
+      <c r="BG6" s="115"/>
+      <c r="BH6" s="115"/>
+      <c r="BI6" s="115"/>
+      <c r="BJ6" s="115"/>
+      <c r="BK6" s="115">
         <f>BF6+7</f>
         <v>45838</v>
       </c>
-      <c r="BL6" s="113"/>
-      <c r="BM6" s="113"/>
-      <c r="BN6" s="113"/>
-      <c r="BO6" s="113"/>
-      <c r="BP6" s="113">
+      <c r="BL6" s="115"/>
+      <c r="BM6" s="115"/>
+      <c r="BN6" s="115"/>
+      <c r="BO6" s="115"/>
+      <c r="BP6" s="115">
         <f>BK6+7</f>
         <v>45845</v>
       </c>
-      <c r="BQ6" s="113"/>
-      <c r="BR6" s="113"/>
-      <c r="BS6" s="113"/>
-      <c r="BT6" s="113"/>
-      <c r="BU6" s="113">
+      <c r="BQ6" s="115"/>
+      <c r="BR6" s="115"/>
+      <c r="BS6" s="115"/>
+      <c r="BT6" s="115"/>
+      <c r="BU6" s="115">
         <f>BP6+7</f>
         <v>45852</v>
       </c>
-      <c r="BV6" s="113"/>
-      <c r="BW6" s="113"/>
-      <c r="BX6" s="113"/>
-      <c r="BY6" s="113"/>
-      <c r="BZ6" s="113">
+      <c r="BV6" s="115"/>
+      <c r="BW6" s="115"/>
+      <c r="BX6" s="115"/>
+      <c r="BY6" s="115"/>
+      <c r="BZ6" s="115">
         <f>BU6+7</f>
         <v>45859</v>
       </c>
-      <c r="CA6" s="113"/>
-      <c r="CB6" s="113"/>
-      <c r="CC6" s="113"/>
-      <c r="CD6" s="113"/>
-      <c r="CE6" s="113">
+      <c r="CA6" s="115"/>
+      <c r="CB6" s="115"/>
+      <c r="CC6" s="115"/>
+      <c r="CD6" s="115"/>
+      <c r="CE6" s="115">
         <f>BZ6+7</f>
         <v>45866</v>
       </c>
-      <c r="CF6" s="113"/>
-      <c r="CG6" s="113"/>
-      <c r="CH6" s="113"/>
-      <c r="CI6" s="113"/>
-      <c r="CJ6" s="113">
+      <c r="CF6" s="115"/>
+      <c r="CG6" s="115"/>
+      <c r="CH6" s="115"/>
+      <c r="CI6" s="115"/>
+      <c r="CJ6" s="115">
         <f>CE6+7</f>
         <v>45873</v>
       </c>
-      <c r="CK6" s="113"/>
-      <c r="CL6" s="113"/>
-      <c r="CM6" s="113"/>
-      <c r="CN6" s="113"/>
+      <c r="CK6" s="115"/>
+      <c r="CL6" s="115"/>
+      <c r="CM6" s="115"/>
+      <c r="CN6" s="115"/>
     </row>
     <row r="7" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="122" t="s">
+      <c r="D7" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="123"/>
-      <c r="F7" s="124" t="s">
+      <c r="E7" s="124"/>
+      <c r="F7" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="123"/>
+      <c r="G7" s="124"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>45761</v>
@@ -6033,18 +6036,6 @@
   </sheetData>
   <sheetProtection password="DF87" sheet="1" insertRows="0"/>
   <mergeCells count="28">
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="AG6:AK6"/>
-    <mergeCell ref="AL6:AP6"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
     <mergeCell ref="BU6:BY6"/>
     <mergeCell ref="BZ6:CD6"/>
     <mergeCell ref="CE6:CI6"/>
@@ -6061,6 +6052,18 @@
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB6:AF6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="AG6:AK6"/>
+    <mergeCell ref="AL6:AP6"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G34">
@@ -6136,15 +6139,15 @@
       <c r="G1" s="114"/>
     </row>
     <row r="2" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -6152,15 +6155,15 @@
       <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="115" t="s">
+      <c r="A3" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -6168,15 +6171,15 @@
       <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="115" t="s">
+      <c r="A4" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="115"/>
-      <c r="C4" s="115"/>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -6184,10 +6187,10 @@
       <c r="L4" s="83"/>
     </row>
     <row r="5" spans="1:92" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
       <c r="AU5" s="1" t="s">
         <v>5</v>
       </c>
@@ -6200,161 +6203,161 @@
     </row>
     <row r="6" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="113">
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="115">
         <f>H7</f>
         <v>45761</v>
       </c>
-      <c r="I6" s="113"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="113"/>
-      <c r="L6" s="113"/>
-      <c r="M6" s="113">
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115">
         <f>H6+7</f>
         <v>45768</v>
       </c>
-      <c r="N6" s="113"/>
-      <c r="O6" s="113"/>
-      <c r="P6" s="113"/>
-      <c r="Q6" s="113"/>
-      <c r="R6" s="113">
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="115">
         <f>M6+7</f>
         <v>45775</v>
       </c>
-      <c r="S6" s="113"/>
-      <c r="T6" s="113"/>
-      <c r="U6" s="113"/>
-      <c r="V6" s="113"/>
-      <c r="W6" s="113">
+      <c r="S6" s="115"/>
+      <c r="T6" s="115"/>
+      <c r="U6" s="115"/>
+      <c r="V6" s="115"/>
+      <c r="W6" s="115">
         <f>R6+7</f>
         <v>45782</v>
       </c>
-      <c r="X6" s="113"/>
-      <c r="Y6" s="113"/>
-      <c r="Z6" s="113"/>
-      <c r="AA6" s="113"/>
-      <c r="AB6" s="113">
+      <c r="X6" s="115"/>
+      <c r="Y6" s="115"/>
+      <c r="Z6" s="115"/>
+      <c r="AA6" s="115"/>
+      <c r="AB6" s="115">
         <f>W6+7</f>
         <v>45789</v>
       </c>
-      <c r="AC6" s="113"/>
-      <c r="AD6" s="113"/>
-      <c r="AE6" s="113"/>
-      <c r="AF6" s="113"/>
-      <c r="AG6" s="113">
+      <c r="AC6" s="115"/>
+      <c r="AD6" s="115"/>
+      <c r="AE6" s="115"/>
+      <c r="AF6" s="115"/>
+      <c r="AG6" s="115">
         <f>AB6+7</f>
         <v>45796</v>
       </c>
-      <c r="AH6" s="113"/>
-      <c r="AI6" s="113"/>
-      <c r="AJ6" s="113"/>
-      <c r="AK6" s="113"/>
-      <c r="AL6" s="113">
+      <c r="AH6" s="115"/>
+      <c r="AI6" s="115"/>
+      <c r="AJ6" s="115"/>
+      <c r="AK6" s="115"/>
+      <c r="AL6" s="115">
         <f>AG6+7</f>
         <v>45803</v>
       </c>
-      <c r="AM6" s="113"/>
-      <c r="AN6" s="113"/>
-      <c r="AO6" s="113"/>
-      <c r="AP6" s="113"/>
-      <c r="AQ6" s="113">
+      <c r="AM6" s="115"/>
+      <c r="AN6" s="115"/>
+      <c r="AO6" s="115"/>
+      <c r="AP6" s="115"/>
+      <c r="AQ6" s="115">
         <f>AL6+7</f>
         <v>45810</v>
       </c>
-      <c r="AR6" s="113"/>
-      <c r="AS6" s="113"/>
-      <c r="AT6" s="113"/>
-      <c r="AU6" s="113"/>
-      <c r="AV6" s="113">
+      <c r="AR6" s="115"/>
+      <c r="AS6" s="115"/>
+      <c r="AT6" s="115"/>
+      <c r="AU6" s="115"/>
+      <c r="AV6" s="115">
         <f>AQ6+7</f>
         <v>45817</v>
       </c>
-      <c r="AW6" s="113"/>
-      <c r="AX6" s="113"/>
-      <c r="AY6" s="113"/>
-      <c r="AZ6" s="113"/>
-      <c r="BA6" s="113">
+      <c r="AW6" s="115"/>
+      <c r="AX6" s="115"/>
+      <c r="AY6" s="115"/>
+      <c r="AZ6" s="115"/>
+      <c r="BA6" s="115">
         <f>AV6+7</f>
         <v>45824</v>
       </c>
-      <c r="BB6" s="113"/>
-      <c r="BC6" s="113"/>
-      <c r="BD6" s="113"/>
-      <c r="BE6" s="113"/>
-      <c r="BF6" s="113">
+      <c r="BB6" s="115"/>
+      <c r="BC6" s="115"/>
+      <c r="BD6" s="115"/>
+      <c r="BE6" s="115"/>
+      <c r="BF6" s="115">
         <f>BA6+7</f>
         <v>45831</v>
       </c>
-      <c r="BG6" s="113"/>
-      <c r="BH6" s="113"/>
-      <c r="BI6" s="113"/>
-      <c r="BJ6" s="113"/>
-      <c r="BK6" s="113">
+      <c r="BG6" s="115"/>
+      <c r="BH6" s="115"/>
+      <c r="BI6" s="115"/>
+      <c r="BJ6" s="115"/>
+      <c r="BK6" s="115">
         <f>BF6+7</f>
         <v>45838</v>
       </c>
-      <c r="BL6" s="113"/>
-      <c r="BM6" s="113"/>
-      <c r="BN6" s="113"/>
-      <c r="BO6" s="113"/>
-      <c r="BP6" s="113">
+      <c r="BL6" s="115"/>
+      <c r="BM6" s="115"/>
+      <c r="BN6" s="115"/>
+      <c r="BO6" s="115"/>
+      <c r="BP6" s="115">
         <f>BK6+7</f>
         <v>45845</v>
       </c>
-      <c r="BQ6" s="113"/>
-      <c r="BR6" s="113"/>
-      <c r="BS6" s="113"/>
-      <c r="BT6" s="113"/>
-      <c r="BU6" s="113">
+      <c r="BQ6" s="115"/>
+      <c r="BR6" s="115"/>
+      <c r="BS6" s="115"/>
+      <c r="BT6" s="115"/>
+      <c r="BU6" s="115">
         <f>BP6+7</f>
         <v>45852</v>
       </c>
-      <c r="BV6" s="113"/>
-      <c r="BW6" s="113"/>
-      <c r="BX6" s="113"/>
-      <c r="BY6" s="113"/>
-      <c r="BZ6" s="113">
+      <c r="BV6" s="115"/>
+      <c r="BW6" s="115"/>
+      <c r="BX6" s="115"/>
+      <c r="BY6" s="115"/>
+      <c r="BZ6" s="115">
         <f>BU6+7</f>
         <v>45859</v>
       </c>
-      <c r="CA6" s="113"/>
-      <c r="CB6" s="113"/>
-      <c r="CC6" s="113"/>
-      <c r="CD6" s="113"/>
-      <c r="CE6" s="113">
+      <c r="CA6" s="115"/>
+      <c r="CB6" s="115"/>
+      <c r="CC6" s="115"/>
+      <c r="CD6" s="115"/>
+      <c r="CE6" s="115">
         <f>BZ6+7</f>
         <v>45866</v>
       </c>
-      <c r="CF6" s="113"/>
-      <c r="CG6" s="113"/>
-      <c r="CH6" s="113"/>
-      <c r="CI6" s="113"/>
-      <c r="CJ6" s="113">
+      <c r="CF6" s="115"/>
+      <c r="CG6" s="115"/>
+      <c r="CH6" s="115"/>
+      <c r="CI6" s="115"/>
+      <c r="CJ6" s="115">
         <f>CE6+7</f>
         <v>45873</v>
       </c>
-      <c r="CK6" s="113"/>
-      <c r="CL6" s="113"/>
-      <c r="CM6" s="113"/>
-      <c r="CN6" s="113"/>
+      <c r="CK6" s="115"/>
+      <c r="CL6" s="115"/>
+      <c r="CM6" s="115"/>
+      <c r="CN6" s="115"/>
     </row>
     <row r="7" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="122" t="s">
+      <c r="D7" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="123"/>
-      <c r="F7" s="124" t="s">
+      <c r="E7" s="124"/>
+      <c r="F7" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="123"/>
+      <c r="G7" s="124"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>45761</v>
@@ -9851,6 +9854,18 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="28">
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -9867,18 +9882,6 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G35">
@@ -10002,15 +10005,15 @@
       <c r="CN1" s="1"/>
     </row>
     <row r="2" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -10098,15 +10101,15 @@
       <c r="CN2" s="1"/>
     </row>
     <row r="3" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A3" s="115" t="s">
+      <c r="A3" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -10194,15 +10197,15 @@
       <c r="CN3" s="1"/>
     </row>
     <row r="4" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A4" s="115" t="s">
+      <c r="A4" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="115"/>
-      <c r="C4" s="115"/>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -10293,10 +10296,10 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -10391,161 +10394,161 @@
     </row>
     <row r="6" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="113">
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="115">
         <f>H7</f>
         <v>46279</v>
       </c>
-      <c r="I6" s="113"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="113"/>
-      <c r="L6" s="113"/>
-      <c r="M6" s="113">
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115">
         <f>H6+7</f>
         <v>46286</v>
       </c>
-      <c r="N6" s="113"/>
-      <c r="O6" s="113"/>
-      <c r="P6" s="113"/>
-      <c r="Q6" s="113"/>
-      <c r="R6" s="113">
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="115">
         <f>M6+7</f>
         <v>46293</v>
       </c>
-      <c r="S6" s="113"/>
-      <c r="T6" s="113"/>
-      <c r="U6" s="113"/>
-      <c r="V6" s="113"/>
-      <c r="W6" s="113">
+      <c r="S6" s="115"/>
+      <c r="T6" s="115"/>
+      <c r="U6" s="115"/>
+      <c r="V6" s="115"/>
+      <c r="W6" s="115">
         <f>R6+7</f>
         <v>46300</v>
       </c>
-      <c r="X6" s="113"/>
-      <c r="Y6" s="113"/>
-      <c r="Z6" s="113"/>
-      <c r="AA6" s="113"/>
-      <c r="AB6" s="113">
+      <c r="X6" s="115"/>
+      <c r="Y6" s="115"/>
+      <c r="Z6" s="115"/>
+      <c r="AA6" s="115"/>
+      <c r="AB6" s="115">
         <f>W6+7</f>
         <v>46307</v>
       </c>
-      <c r="AC6" s="113"/>
-      <c r="AD6" s="113"/>
-      <c r="AE6" s="113"/>
-      <c r="AF6" s="113"/>
-      <c r="AG6" s="113">
+      <c r="AC6" s="115"/>
+      <c r="AD6" s="115"/>
+      <c r="AE6" s="115"/>
+      <c r="AF6" s="115"/>
+      <c r="AG6" s="115">
         <f>AB6+7</f>
         <v>46314</v>
       </c>
-      <c r="AH6" s="113"/>
-      <c r="AI6" s="113"/>
-      <c r="AJ6" s="113"/>
-      <c r="AK6" s="113"/>
-      <c r="AL6" s="113">
+      <c r="AH6" s="115"/>
+      <c r="AI6" s="115"/>
+      <c r="AJ6" s="115"/>
+      <c r="AK6" s="115"/>
+      <c r="AL6" s="115">
         <f>AG6+7</f>
         <v>46321</v>
       </c>
-      <c r="AM6" s="113"/>
-      <c r="AN6" s="113"/>
-      <c r="AO6" s="113"/>
-      <c r="AP6" s="113"/>
-      <c r="AQ6" s="113">
+      <c r="AM6" s="115"/>
+      <c r="AN6" s="115"/>
+      <c r="AO6" s="115"/>
+      <c r="AP6" s="115"/>
+      <c r="AQ6" s="115">
         <f>AL6+7</f>
         <v>46328</v>
       </c>
-      <c r="AR6" s="113"/>
-      <c r="AS6" s="113"/>
-      <c r="AT6" s="113"/>
-      <c r="AU6" s="113"/>
-      <c r="AV6" s="113">
+      <c r="AR6" s="115"/>
+      <c r="AS6" s="115"/>
+      <c r="AT6" s="115"/>
+      <c r="AU6" s="115"/>
+      <c r="AV6" s="115">
         <f>AQ6+7</f>
         <v>46335</v>
       </c>
-      <c r="AW6" s="113"/>
-      <c r="AX6" s="113"/>
-      <c r="AY6" s="113"/>
-      <c r="AZ6" s="113"/>
-      <c r="BA6" s="113">
+      <c r="AW6" s="115"/>
+      <c r="AX6" s="115"/>
+      <c r="AY6" s="115"/>
+      <c r="AZ6" s="115"/>
+      <c r="BA6" s="115">
         <f>AV6+7</f>
         <v>46342</v>
       </c>
-      <c r="BB6" s="113"/>
-      <c r="BC6" s="113"/>
-      <c r="BD6" s="113"/>
-      <c r="BE6" s="113"/>
-      <c r="BF6" s="113">
+      <c r="BB6" s="115"/>
+      <c r="BC6" s="115"/>
+      <c r="BD6" s="115"/>
+      <c r="BE6" s="115"/>
+      <c r="BF6" s="115">
         <f>BA6+7</f>
         <v>46349</v>
       </c>
-      <c r="BG6" s="113"/>
-      <c r="BH6" s="113"/>
-      <c r="BI6" s="113"/>
-      <c r="BJ6" s="113"/>
-      <c r="BK6" s="113">
+      <c r="BG6" s="115"/>
+      <c r="BH6" s="115"/>
+      <c r="BI6" s="115"/>
+      <c r="BJ6" s="115"/>
+      <c r="BK6" s="115">
         <f>BF6+7</f>
         <v>46356</v>
       </c>
-      <c r="BL6" s="113"/>
-      <c r="BM6" s="113"/>
-      <c r="BN6" s="113"/>
-      <c r="BO6" s="113"/>
-      <c r="BP6" s="113">
+      <c r="BL6" s="115"/>
+      <c r="BM6" s="115"/>
+      <c r="BN6" s="115"/>
+      <c r="BO6" s="115"/>
+      <c r="BP6" s="115">
         <f>BK6+7</f>
         <v>46363</v>
       </c>
-      <c r="BQ6" s="113"/>
-      <c r="BR6" s="113"/>
-      <c r="BS6" s="113"/>
-      <c r="BT6" s="113"/>
-      <c r="BU6" s="113">
+      <c r="BQ6" s="115"/>
+      <c r="BR6" s="115"/>
+      <c r="BS6" s="115"/>
+      <c r="BT6" s="115"/>
+      <c r="BU6" s="115">
         <f>BP6+7</f>
         <v>46370</v>
       </c>
-      <c r="BV6" s="113"/>
-      <c r="BW6" s="113"/>
-      <c r="BX6" s="113"/>
-      <c r="BY6" s="113"/>
-      <c r="BZ6" s="113">
+      <c r="BV6" s="115"/>
+      <c r="BW6" s="115"/>
+      <c r="BX6" s="115"/>
+      <c r="BY6" s="115"/>
+      <c r="BZ6" s="115">
         <f>BU6+7</f>
         <v>46377</v>
       </c>
-      <c r="CA6" s="113"/>
-      <c r="CB6" s="113"/>
-      <c r="CC6" s="113"/>
-      <c r="CD6" s="113"/>
-      <c r="CE6" s="113">
+      <c r="CA6" s="115"/>
+      <c r="CB6" s="115"/>
+      <c r="CC6" s="115"/>
+      <c r="CD6" s="115"/>
+      <c r="CE6" s="115">
         <f>BZ6+7</f>
         <v>46384</v>
       </c>
-      <c r="CF6" s="113"/>
-      <c r="CG6" s="113"/>
-      <c r="CH6" s="113"/>
-      <c r="CI6" s="113"/>
-      <c r="CJ6" s="113">
+      <c r="CF6" s="115"/>
+      <c r="CG6" s="115"/>
+      <c r="CH6" s="115"/>
+      <c r="CI6" s="115"/>
+      <c r="CJ6" s="115">
         <f>CE6+7</f>
         <v>46391</v>
       </c>
-      <c r="CK6" s="113"/>
-      <c r="CL6" s="113"/>
-      <c r="CM6" s="113"/>
-      <c r="CN6" s="113"/>
+      <c r="CK6" s="115"/>
+      <c r="CL6" s="115"/>
+      <c r="CM6" s="115"/>
+      <c r="CN6" s="115"/>
     </row>
     <row r="7" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="122" t="s">
+      <c r="D7" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="123"/>
-      <c r="F7" s="124" t="s">
+      <c r="E7" s="124"/>
+      <c r="F7" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="123"/>
+      <c r="G7" s="124"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>46279</v>
@@ -12218,7 +12221,7 @@
       <c r="CN19" s="22"/>
     </row>
     <row r="20" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A20" s="125" t="s">
+      <c r="A20" s="113" t="s">
         <v>78</v>
       </c>
       <c r="B20" s="23"/>
@@ -12410,7 +12413,7 @@
       <c r="CN21" s="28"/>
     </row>
     <row r="22" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A22" s="125" t="s">
+      <c r="A22" s="113" t="s">
         <v>79</v>
       </c>
       <c r="B22" s="23"/>
@@ -12698,7 +12701,7 @@
       <c r="CN24" s="28"/>
     </row>
     <row r="25" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A25" s="125" t="s">
+      <c r="A25" s="113" t="s">
         <v>80</v>
       </c>
       <c r="B25" s="23"/>
@@ -13180,7 +13183,7 @@
       <c r="CN29" s="28"/>
     </row>
     <row r="30" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A30" s="125" t="s">
+      <c r="A30" s="113" t="s">
         <v>88</v>
       </c>
       <c r="B30" s="23"/>
@@ -13564,7 +13567,7 @@
       <c r="CN33" s="28"/>
     </row>
     <row r="34" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A34" s="125" t="s">
+      <c r="A34" s="113" t="s">
         <v>92</v>
       </c>
       <c r="B34" s="23"/>
@@ -15301,6 +15304,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -15317,18 +15332,6 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="G43:G44 F9:G41">
@@ -15342,6 +15345,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A6A6C361903FA540AF4D79E6EA2B777C" ma:contentTypeVersion="18" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ea7c12cc56e366ff4dda5c6e96eadaab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaa52e1c-8772-4366-aa63-bf636c80ebd4" xmlns:ns3="0c73c1f5-50cd-4477-a315-44bef7b8a847" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7966d967ae6f075ad6e4da9e3740ee6a" ns2:_="" ns3:_="">
     <xsd:import namespace="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
@@ -15596,34 +15626,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8D2A65F-21CC-403E-82EF-9B2DA85938F8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15640,23 +15662,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/資料/ガントチャート_4GA3_遠藤直樹.xlsx
+++ b/資料/ガントチャート_4GA3_遠藤直樹.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBC25EC-7050-4B43-991F-613559887970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16A0477-2C48-445D-A36F-A0D59317C504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5175" yWindow="3600" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="制作進捗確認表" sheetId="16" state="hidden" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="96">
   <si>
     <t>企画制作　進捗管理表</t>
     <phoneticPr fontId="19"/>
@@ -604,6 +604,10 @@
     <rPh sb="9" eb="12">
       <t>シンエイタイ</t>
     </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>マップシーン</t>
     <phoneticPr fontId="19"/>
   </si>
 </sst>
@@ -1861,11 +1865,20 @@
       <alignment horizontal="left" indent="1" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -1887,15 +1900,6 @@
     </xf>
     <xf numFmtId="183" fontId="23" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2487,22 +2491,22 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="114">
+      <c r="E1" s="118">
         <v>45761</v>
       </c>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
     </row>
     <row r="2" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -2510,15 +2514,15 @@
       <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -2526,15 +2530,15 @@
       <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -2542,10 +2546,10 @@
       <c r="L4" s="83"/>
     </row>
     <row r="5" spans="1:92" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
       <c r="AU5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2558,161 +2562,161 @@
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="115">
+      <c r="B6" s="125"/>
+      <c r="C6" s="125"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="114">
         <f>H7</f>
         <v>45761</v>
       </c>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="115">
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
+      <c r="M6" s="114">
         <f>H6+7</f>
         <v>45768</v>
       </c>
-      <c r="N6" s="115"/>
-      <c r="O6" s="115"/>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="115"/>
-      <c r="R6" s="115">
+      <c r="N6" s="114"/>
+      <c r="O6" s="114"/>
+      <c r="P6" s="114"/>
+      <c r="Q6" s="114"/>
+      <c r="R6" s="114">
         <f>M6+7</f>
         <v>45775</v>
       </c>
-      <c r="S6" s="115"/>
-      <c r="T6" s="115"/>
-      <c r="U6" s="115"/>
-      <c r="V6" s="115"/>
-      <c r="W6" s="115">
+      <c r="S6" s="114"/>
+      <c r="T6" s="114"/>
+      <c r="U6" s="114"/>
+      <c r="V6" s="114"/>
+      <c r="W6" s="114">
         <f>R6+7</f>
         <v>45782</v>
       </c>
-      <c r="X6" s="115"/>
-      <c r="Y6" s="115"/>
-      <c r="Z6" s="115"/>
-      <c r="AA6" s="115"/>
-      <c r="AB6" s="115">
+      <c r="X6" s="114"/>
+      <c r="Y6" s="114"/>
+      <c r="Z6" s="114"/>
+      <c r="AA6" s="114"/>
+      <c r="AB6" s="114">
         <f>W6+7</f>
         <v>45789</v>
       </c>
-      <c r="AC6" s="115"/>
-      <c r="AD6" s="115"/>
-      <c r="AE6" s="115"/>
-      <c r="AF6" s="115"/>
-      <c r="AG6" s="115">
+      <c r="AC6" s="114"/>
+      <c r="AD6" s="114"/>
+      <c r="AE6" s="114"/>
+      <c r="AF6" s="114"/>
+      <c r="AG6" s="114">
         <f>AB6+7</f>
         <v>45796</v>
       </c>
-      <c r="AH6" s="115"/>
-      <c r="AI6" s="115"/>
-      <c r="AJ6" s="115"/>
-      <c r="AK6" s="115"/>
-      <c r="AL6" s="115">
+      <c r="AH6" s="114"/>
+      <c r="AI6" s="114"/>
+      <c r="AJ6" s="114"/>
+      <c r="AK6" s="114"/>
+      <c r="AL6" s="114">
         <f>AG6+7</f>
         <v>45803</v>
       </c>
-      <c r="AM6" s="115"/>
-      <c r="AN6" s="115"/>
-      <c r="AO6" s="115"/>
-      <c r="AP6" s="115"/>
-      <c r="AQ6" s="115">
+      <c r="AM6" s="114"/>
+      <c r="AN6" s="114"/>
+      <c r="AO6" s="114"/>
+      <c r="AP6" s="114"/>
+      <c r="AQ6" s="114">
         <f>AL6+7</f>
         <v>45810</v>
       </c>
-      <c r="AR6" s="115"/>
-      <c r="AS6" s="115"/>
-      <c r="AT6" s="115"/>
-      <c r="AU6" s="115"/>
-      <c r="AV6" s="115">
+      <c r="AR6" s="114"/>
+      <c r="AS6" s="114"/>
+      <c r="AT6" s="114"/>
+      <c r="AU6" s="114"/>
+      <c r="AV6" s="114">
         <f>AQ6+7</f>
         <v>45817</v>
       </c>
-      <c r="AW6" s="115"/>
-      <c r="AX6" s="115"/>
-      <c r="AY6" s="115"/>
-      <c r="AZ6" s="115"/>
-      <c r="BA6" s="115">
+      <c r="AW6" s="114"/>
+      <c r="AX6" s="114"/>
+      <c r="AY6" s="114"/>
+      <c r="AZ6" s="114"/>
+      <c r="BA6" s="114">
         <f>AV6+7</f>
         <v>45824</v>
       </c>
-      <c r="BB6" s="115"/>
-      <c r="BC6" s="115"/>
-      <c r="BD6" s="115"/>
-      <c r="BE6" s="115"/>
-      <c r="BF6" s="115">
+      <c r="BB6" s="114"/>
+      <c r="BC6" s="114"/>
+      <c r="BD6" s="114"/>
+      <c r="BE6" s="114"/>
+      <c r="BF6" s="114">
         <f>BA6+7</f>
         <v>45831</v>
       </c>
-      <c r="BG6" s="115"/>
-      <c r="BH6" s="115"/>
-      <c r="BI6" s="115"/>
-      <c r="BJ6" s="115"/>
-      <c r="BK6" s="115">
+      <c r="BG6" s="114"/>
+      <c r="BH6" s="114"/>
+      <c r="BI6" s="114"/>
+      <c r="BJ6" s="114"/>
+      <c r="BK6" s="114">
         <f>BF6+7</f>
         <v>45838</v>
       </c>
-      <c r="BL6" s="115"/>
-      <c r="BM6" s="115"/>
-      <c r="BN6" s="115"/>
-      <c r="BO6" s="115"/>
-      <c r="BP6" s="115">
+      <c r="BL6" s="114"/>
+      <c r="BM6" s="114"/>
+      <c r="BN6" s="114"/>
+      <c r="BO6" s="114"/>
+      <c r="BP6" s="114">
         <f>BK6+7</f>
         <v>45845</v>
       </c>
-      <c r="BQ6" s="115"/>
-      <c r="BR6" s="115"/>
-      <c r="BS6" s="115"/>
-      <c r="BT6" s="115"/>
-      <c r="BU6" s="115">
+      <c r="BQ6" s="114"/>
+      <c r="BR6" s="114"/>
+      <c r="BS6" s="114"/>
+      <c r="BT6" s="114"/>
+      <c r="BU6" s="114">
         <f>BP6+7</f>
         <v>45852</v>
       </c>
-      <c r="BV6" s="115"/>
-      <c r="BW6" s="115"/>
-      <c r="BX6" s="115"/>
-      <c r="BY6" s="115"/>
-      <c r="BZ6" s="115">
+      <c r="BV6" s="114"/>
+      <c r="BW6" s="114"/>
+      <c r="BX6" s="114"/>
+      <c r="BY6" s="114"/>
+      <c r="BZ6" s="114">
         <f>BU6+7</f>
         <v>45859</v>
       </c>
-      <c r="CA6" s="115"/>
-      <c r="CB6" s="115"/>
-      <c r="CC6" s="115"/>
-      <c r="CD6" s="115"/>
-      <c r="CE6" s="115">
+      <c r="CA6" s="114"/>
+      <c r="CB6" s="114"/>
+      <c r="CC6" s="114"/>
+      <c r="CD6" s="114"/>
+      <c r="CE6" s="114">
         <f>BZ6+7</f>
         <v>45866</v>
       </c>
-      <c r="CF6" s="115"/>
-      <c r="CG6" s="115"/>
-      <c r="CH6" s="115"/>
-      <c r="CI6" s="115"/>
-      <c r="CJ6" s="115">
+      <c r="CF6" s="114"/>
+      <c r="CG6" s="114"/>
+      <c r="CH6" s="114"/>
+      <c r="CI6" s="114"/>
+      <c r="CJ6" s="114">
         <f>CE6+7</f>
         <v>45873</v>
       </c>
-      <c r="CK6" s="115"/>
-      <c r="CL6" s="115"/>
-      <c r="CM6" s="115"/>
-      <c r="CN6" s="115"/>
+      <c r="CK6" s="114"/>
+      <c r="CL6" s="114"/>
+      <c r="CM6" s="114"/>
+      <c r="CN6" s="114"/>
     </row>
     <row r="7" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="123" t="s">
+      <c r="D7" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="124"/>
-      <c r="F7" s="125" t="s">
+      <c r="E7" s="116"/>
+      <c r="F7" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="124"/>
+      <c r="G7" s="116"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>45761</v>
@@ -6036,6 +6040,18 @@
   </sheetData>
   <sheetProtection password="DF87" sheet="1" insertRows="0"/>
   <mergeCells count="28">
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="AG6:AK6"/>
+    <mergeCell ref="AL6:AP6"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="BU6:BY6"/>
     <mergeCell ref="BZ6:CD6"/>
     <mergeCell ref="CE6:CI6"/>
@@ -6052,18 +6068,6 @@
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB6:AF6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="AG6:AK6"/>
-    <mergeCell ref="AL6:AP6"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G34">
@@ -6132,22 +6136,22 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="114">
+      <c r="E1" s="118">
         <v>45761</v>
       </c>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
     </row>
     <row r="2" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -6155,15 +6159,15 @@
       <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -6171,15 +6175,15 @@
       <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -6187,10 +6191,10 @@
       <c r="L4" s="83"/>
     </row>
     <row r="5" spans="1:92" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
       <c r="AU5" s="1" t="s">
         <v>5</v>
       </c>
@@ -6203,161 +6207,161 @@
     </row>
     <row r="6" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="115">
+      <c r="B6" s="125"/>
+      <c r="C6" s="125"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="114">
         <f>H7</f>
         <v>45761</v>
       </c>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="115">
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
+      <c r="M6" s="114">
         <f>H6+7</f>
         <v>45768</v>
       </c>
-      <c r="N6" s="115"/>
-      <c r="O6" s="115"/>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="115"/>
-      <c r="R6" s="115">
+      <c r="N6" s="114"/>
+      <c r="O6" s="114"/>
+      <c r="P6" s="114"/>
+      <c r="Q6" s="114"/>
+      <c r="R6" s="114">
         <f>M6+7</f>
         <v>45775</v>
       </c>
-      <c r="S6" s="115"/>
-      <c r="T6" s="115"/>
-      <c r="U6" s="115"/>
-      <c r="V6" s="115"/>
-      <c r="W6" s="115">
+      <c r="S6" s="114"/>
+      <c r="T6" s="114"/>
+      <c r="U6" s="114"/>
+      <c r="V6" s="114"/>
+      <c r="W6" s="114">
         <f>R6+7</f>
         <v>45782</v>
       </c>
-      <c r="X6" s="115"/>
-      <c r="Y6" s="115"/>
-      <c r="Z6" s="115"/>
-      <c r="AA6" s="115"/>
-      <c r="AB6" s="115">
+      <c r="X6" s="114"/>
+      <c r="Y6" s="114"/>
+      <c r="Z6" s="114"/>
+      <c r="AA6" s="114"/>
+      <c r="AB6" s="114">
         <f>W6+7</f>
         <v>45789</v>
       </c>
-      <c r="AC6" s="115"/>
-      <c r="AD6" s="115"/>
-      <c r="AE6" s="115"/>
-      <c r="AF6" s="115"/>
-      <c r="AG6" s="115">
+      <c r="AC6" s="114"/>
+      <c r="AD6" s="114"/>
+      <c r="AE6" s="114"/>
+      <c r="AF6" s="114"/>
+      <c r="AG6" s="114">
         <f>AB6+7</f>
         <v>45796</v>
       </c>
-      <c r="AH6" s="115"/>
-      <c r="AI6" s="115"/>
-      <c r="AJ6" s="115"/>
-      <c r="AK6" s="115"/>
-      <c r="AL6" s="115">
+      <c r="AH6" s="114"/>
+      <c r="AI6" s="114"/>
+      <c r="AJ6" s="114"/>
+      <c r="AK6" s="114"/>
+      <c r="AL6" s="114">
         <f>AG6+7</f>
         <v>45803</v>
       </c>
-      <c r="AM6" s="115"/>
-      <c r="AN6" s="115"/>
-      <c r="AO6" s="115"/>
-      <c r="AP6" s="115"/>
-      <c r="AQ6" s="115">
+      <c r="AM6" s="114"/>
+      <c r="AN6" s="114"/>
+      <c r="AO6" s="114"/>
+      <c r="AP6" s="114"/>
+      <c r="AQ6" s="114">
         <f>AL6+7</f>
         <v>45810</v>
       </c>
-      <c r="AR6" s="115"/>
-      <c r="AS6" s="115"/>
-      <c r="AT6" s="115"/>
-      <c r="AU6" s="115"/>
-      <c r="AV6" s="115">
+      <c r="AR6" s="114"/>
+      <c r="AS6" s="114"/>
+      <c r="AT6" s="114"/>
+      <c r="AU6" s="114"/>
+      <c r="AV6" s="114">
         <f>AQ6+7</f>
         <v>45817</v>
       </c>
-      <c r="AW6" s="115"/>
-      <c r="AX6" s="115"/>
-      <c r="AY6" s="115"/>
-      <c r="AZ6" s="115"/>
-      <c r="BA6" s="115">
+      <c r="AW6" s="114"/>
+      <c r="AX6" s="114"/>
+      <c r="AY6" s="114"/>
+      <c r="AZ6" s="114"/>
+      <c r="BA6" s="114">
         <f>AV6+7</f>
         <v>45824</v>
       </c>
-      <c r="BB6" s="115"/>
-      <c r="BC6" s="115"/>
-      <c r="BD6" s="115"/>
-      <c r="BE6" s="115"/>
-      <c r="BF6" s="115">
+      <c r="BB6" s="114"/>
+      <c r="BC6" s="114"/>
+      <c r="BD6" s="114"/>
+      <c r="BE6" s="114"/>
+      <c r="BF6" s="114">
         <f>BA6+7</f>
         <v>45831</v>
       </c>
-      <c r="BG6" s="115"/>
-      <c r="BH6" s="115"/>
-      <c r="BI6" s="115"/>
-      <c r="BJ6" s="115"/>
-      <c r="BK6" s="115">
+      <c r="BG6" s="114"/>
+      <c r="BH6" s="114"/>
+      <c r="BI6" s="114"/>
+      <c r="BJ6" s="114"/>
+      <c r="BK6" s="114">
         <f>BF6+7</f>
         <v>45838</v>
       </c>
-      <c r="BL6" s="115"/>
-      <c r="BM6" s="115"/>
-      <c r="BN6" s="115"/>
-      <c r="BO6" s="115"/>
-      <c r="BP6" s="115">
+      <c r="BL6" s="114"/>
+      <c r="BM6" s="114"/>
+      <c r="BN6" s="114"/>
+      <c r="BO6" s="114"/>
+      <c r="BP6" s="114">
         <f>BK6+7</f>
         <v>45845</v>
       </c>
-      <c r="BQ6" s="115"/>
-      <c r="BR6" s="115"/>
-      <c r="BS6" s="115"/>
-      <c r="BT6" s="115"/>
-      <c r="BU6" s="115">
+      <c r="BQ6" s="114"/>
+      <c r="BR6" s="114"/>
+      <c r="BS6" s="114"/>
+      <c r="BT6" s="114"/>
+      <c r="BU6" s="114">
         <f>BP6+7</f>
         <v>45852</v>
       </c>
-      <c r="BV6" s="115"/>
-      <c r="BW6" s="115"/>
-      <c r="BX6" s="115"/>
-      <c r="BY6" s="115"/>
-      <c r="BZ6" s="115">
+      <c r="BV6" s="114"/>
+      <c r="BW6" s="114"/>
+      <c r="BX6" s="114"/>
+      <c r="BY6" s="114"/>
+      <c r="BZ6" s="114">
         <f>BU6+7</f>
         <v>45859</v>
       </c>
-      <c r="CA6" s="115"/>
-      <c r="CB6" s="115"/>
-      <c r="CC6" s="115"/>
-      <c r="CD6" s="115"/>
-      <c r="CE6" s="115">
+      <c r="CA6" s="114"/>
+      <c r="CB6" s="114"/>
+      <c r="CC6" s="114"/>
+      <c r="CD6" s="114"/>
+      <c r="CE6" s="114">
         <f>BZ6+7</f>
         <v>45866</v>
       </c>
-      <c r="CF6" s="115"/>
-      <c r="CG6" s="115"/>
-      <c r="CH6" s="115"/>
-      <c r="CI6" s="115"/>
-      <c r="CJ6" s="115">
+      <c r="CF6" s="114"/>
+      <c r="CG6" s="114"/>
+      <c r="CH6" s="114"/>
+      <c r="CI6" s="114"/>
+      <c r="CJ6" s="114">
         <f>CE6+7</f>
         <v>45873</v>
       </c>
-      <c r="CK6" s="115"/>
-      <c r="CL6" s="115"/>
-      <c r="CM6" s="115"/>
-      <c r="CN6" s="115"/>
+      <c r="CK6" s="114"/>
+      <c r="CL6" s="114"/>
+      <c r="CM6" s="114"/>
+      <c r="CN6" s="114"/>
     </row>
     <row r="7" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="123" t="s">
+      <c r="D7" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="124"/>
-      <c r="F7" s="125" t="s">
+      <c r="E7" s="116"/>
+      <c r="F7" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="124"/>
+      <c r="G7" s="116"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>45761</v>
@@ -9854,18 +9858,6 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="28">
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -9882,6 +9874,18 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G35">
@@ -9913,11 +9917,11 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="114">
+      <c r="E1" s="118">
         <v>46280</v>
       </c>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -10005,15 +10009,15 @@
       <c r="CN1" s="1"/>
     </row>
     <row r="2" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="119" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -10101,15 +10105,15 @@
       <c r="CN2" s="1"/>
     </row>
     <row r="3" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -10197,15 +10201,15 @@
       <c r="CN3" s="1"/>
     </row>
     <row r="4" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -10296,10 +10300,10 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -10394,161 +10398,161 @@
     </row>
     <row r="6" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="115">
+      <c r="B6" s="125"/>
+      <c r="C6" s="125"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="114">
         <f>H7</f>
         <v>46279</v>
       </c>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="115">
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
+      <c r="M6" s="114">
         <f>H6+7</f>
         <v>46286</v>
       </c>
-      <c r="N6" s="115"/>
-      <c r="O6" s="115"/>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="115"/>
-      <c r="R6" s="115">
+      <c r="N6" s="114"/>
+      <c r="O6" s="114"/>
+      <c r="P6" s="114"/>
+      <c r="Q6" s="114"/>
+      <c r="R6" s="114">
         <f>M6+7</f>
         <v>46293</v>
       </c>
-      <c r="S6" s="115"/>
-      <c r="T6" s="115"/>
-      <c r="U6" s="115"/>
-      <c r="V6" s="115"/>
-      <c r="W6" s="115">
+      <c r="S6" s="114"/>
+      <c r="T6" s="114"/>
+      <c r="U6" s="114"/>
+      <c r="V6" s="114"/>
+      <c r="W6" s="114">
         <f>R6+7</f>
         <v>46300</v>
       </c>
-      <c r="X6" s="115"/>
-      <c r="Y6" s="115"/>
-      <c r="Z6" s="115"/>
-      <c r="AA6" s="115"/>
-      <c r="AB6" s="115">
+      <c r="X6" s="114"/>
+      <c r="Y6" s="114"/>
+      <c r="Z6" s="114"/>
+      <c r="AA6" s="114"/>
+      <c r="AB6" s="114">
         <f>W6+7</f>
         <v>46307</v>
       </c>
-      <c r="AC6" s="115"/>
-      <c r="AD6" s="115"/>
-      <c r="AE6" s="115"/>
-      <c r="AF6" s="115"/>
-      <c r="AG6" s="115">
+      <c r="AC6" s="114"/>
+      <c r="AD6" s="114"/>
+      <c r="AE6" s="114"/>
+      <c r="AF6" s="114"/>
+      <c r="AG6" s="114">
         <f>AB6+7</f>
         <v>46314</v>
       </c>
-      <c r="AH6" s="115"/>
-      <c r="AI6" s="115"/>
-      <c r="AJ6" s="115"/>
-      <c r="AK6" s="115"/>
-      <c r="AL6" s="115">
+      <c r="AH6" s="114"/>
+      <c r="AI6" s="114"/>
+      <c r="AJ6" s="114"/>
+      <c r="AK6" s="114"/>
+      <c r="AL6" s="114">
         <f>AG6+7</f>
         <v>46321</v>
       </c>
-      <c r="AM6" s="115"/>
-      <c r="AN6" s="115"/>
-      <c r="AO6" s="115"/>
-      <c r="AP6" s="115"/>
-      <c r="AQ6" s="115">
+      <c r="AM6" s="114"/>
+      <c r="AN6" s="114"/>
+      <c r="AO6" s="114"/>
+      <c r="AP6" s="114"/>
+      <c r="AQ6" s="114">
         <f>AL6+7</f>
         <v>46328</v>
       </c>
-      <c r="AR6" s="115"/>
-      <c r="AS6" s="115"/>
-      <c r="AT6" s="115"/>
-      <c r="AU6" s="115"/>
-      <c r="AV6" s="115">
+      <c r="AR6" s="114"/>
+      <c r="AS6" s="114"/>
+      <c r="AT6" s="114"/>
+      <c r="AU6" s="114"/>
+      <c r="AV6" s="114">
         <f>AQ6+7</f>
         <v>46335</v>
       </c>
-      <c r="AW6" s="115"/>
-      <c r="AX6" s="115"/>
-      <c r="AY6" s="115"/>
-      <c r="AZ6" s="115"/>
-      <c r="BA6" s="115">
+      <c r="AW6" s="114"/>
+      <c r="AX6" s="114"/>
+      <c r="AY6" s="114"/>
+      <c r="AZ6" s="114"/>
+      <c r="BA6" s="114">
         <f>AV6+7</f>
         <v>46342</v>
       </c>
-      <c r="BB6" s="115"/>
-      <c r="BC6" s="115"/>
-      <c r="BD6" s="115"/>
-      <c r="BE6" s="115"/>
-      <c r="BF6" s="115">
+      <c r="BB6" s="114"/>
+      <c r="BC6" s="114"/>
+      <c r="BD6" s="114"/>
+      <c r="BE6" s="114"/>
+      <c r="BF6" s="114">
         <f>BA6+7</f>
         <v>46349</v>
       </c>
-      <c r="BG6" s="115"/>
-      <c r="BH6" s="115"/>
-      <c r="BI6" s="115"/>
-      <c r="BJ6" s="115"/>
-      <c r="BK6" s="115">
+      <c r="BG6" s="114"/>
+      <c r="BH6" s="114"/>
+      <c r="BI6" s="114"/>
+      <c r="BJ6" s="114"/>
+      <c r="BK6" s="114">
         <f>BF6+7</f>
         <v>46356</v>
       </c>
-      <c r="BL6" s="115"/>
-      <c r="BM6" s="115"/>
-      <c r="BN6" s="115"/>
-      <c r="BO6" s="115"/>
-      <c r="BP6" s="115">
+      <c r="BL6" s="114"/>
+      <c r="BM6" s="114"/>
+      <c r="BN6" s="114"/>
+      <c r="BO6" s="114"/>
+      <c r="BP6" s="114">
         <f>BK6+7</f>
         <v>46363</v>
       </c>
-      <c r="BQ6" s="115"/>
-      <c r="BR6" s="115"/>
-      <c r="BS6" s="115"/>
-      <c r="BT6" s="115"/>
-      <c r="BU6" s="115">
+      <c r="BQ6" s="114"/>
+      <c r="BR6" s="114"/>
+      <c r="BS6" s="114"/>
+      <c r="BT6" s="114"/>
+      <c r="BU6" s="114">
         <f>BP6+7</f>
         <v>46370</v>
       </c>
-      <c r="BV6" s="115"/>
-      <c r="BW6" s="115"/>
-      <c r="BX6" s="115"/>
-      <c r="BY6" s="115"/>
-      <c r="BZ6" s="115">
+      <c r="BV6" s="114"/>
+      <c r="BW6" s="114"/>
+      <c r="BX6" s="114"/>
+      <c r="BY6" s="114"/>
+      <c r="BZ6" s="114">
         <f>BU6+7</f>
         <v>46377</v>
       </c>
-      <c r="CA6" s="115"/>
-      <c r="CB6" s="115"/>
-      <c r="CC6" s="115"/>
-      <c r="CD6" s="115"/>
-      <c r="CE6" s="115">
+      <c r="CA6" s="114"/>
+      <c r="CB6" s="114"/>
+      <c r="CC6" s="114"/>
+      <c r="CD6" s="114"/>
+      <c r="CE6" s="114">
         <f>BZ6+7</f>
         <v>46384</v>
       </c>
-      <c r="CF6" s="115"/>
-      <c r="CG6" s="115"/>
-      <c r="CH6" s="115"/>
-      <c r="CI6" s="115"/>
-      <c r="CJ6" s="115">
+      <c r="CF6" s="114"/>
+      <c r="CG6" s="114"/>
+      <c r="CH6" s="114"/>
+      <c r="CI6" s="114"/>
+      <c r="CJ6" s="114">
         <f>CE6+7</f>
         <v>46391</v>
       </c>
-      <c r="CK6" s="115"/>
-      <c r="CL6" s="115"/>
-      <c r="CM6" s="115"/>
-      <c r="CN6" s="115"/>
+      <c r="CK6" s="114"/>
+      <c r="CL6" s="114"/>
+      <c r="CM6" s="114"/>
+      <c r="CN6" s="114"/>
     </row>
     <row r="7" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="123" t="s">
+      <c r="D7" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="124"/>
-      <c r="F7" s="125" t="s">
+      <c r="E7" s="116"/>
+      <c r="F7" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="124"/>
+      <c r="G7" s="116"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>46279</v>
@@ -11269,11 +11273,21 @@
         <v>65</v>
       </c>
       <c r="B10" s="10"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="C10" s="105">
+        <v>1</v>
+      </c>
+      <c r="D10" s="12">
+        <v>46287</v>
+      </c>
+      <c r="E10" s="12">
+        <v>46290</v>
+      </c>
+      <c r="F10" s="12">
+        <v>46287</v>
+      </c>
+      <c r="G10" s="12">
+        <v>46290</v>
+      </c>
       <c r="H10" s="13"/>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
@@ -11365,10 +11379,18 @@
         <v>66</v>
       </c>
       <c r="B11" s="10"/>
-      <c r="C11" s="105"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="C11" s="105">
+        <v>0.2</v>
+      </c>
+      <c r="D11" s="12">
+        <v>46306</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46315</v>
+      </c>
+      <c r="F11" s="12">
+        <v>46306</v>
+      </c>
       <c r="G11" s="12"/>
       <c r="H11" s="13"/>
       <c r="I11" s="14"/>
@@ -11461,9 +11483,15 @@
         <v>67</v>
       </c>
       <c r="B12" s="10"/>
-      <c r="C12" s="105"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="C12" s="105">
+        <v>0.3</v>
+      </c>
+      <c r="D12" s="12">
+        <v>46306</v>
+      </c>
+      <c r="E12" s="12">
+        <v>46315</v>
+      </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="13"/>
@@ -11557,11 +11585,21 @@
         <v>68</v>
       </c>
       <c r="B13" s="10"/>
-      <c r="C13" s="105"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+      <c r="C13" s="105">
+        <v>1</v>
+      </c>
+      <c r="D13" s="12">
+        <v>46296</v>
+      </c>
+      <c r="E13" s="12">
+        <v>46305</v>
+      </c>
+      <c r="F13" s="12">
+        <v>46296</v>
+      </c>
+      <c r="G13" s="12">
+        <v>46300</v>
+      </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
@@ -11653,10 +11691,18 @@
         <v>69</v>
       </c>
       <c r="B14" s="10"/>
-      <c r="C14" s="105"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="C14" s="105">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="12">
+        <v>46306</v>
+      </c>
+      <c r="E14" s="12">
+        <v>46315</v>
+      </c>
+      <c r="F14" s="12">
+        <v>46306</v>
+      </c>
       <c r="G14" s="12"/>
       <c r="H14" s="13"/>
       <c r="I14" s="14"/>
@@ -11749,11 +11795,21 @@
         <v>70</v>
       </c>
       <c r="B15" s="10"/>
-      <c r="C15" s="105"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
+      <c r="C15" s="105">
+        <v>1</v>
+      </c>
+      <c r="D15" s="12">
+        <v>46300</v>
+      </c>
+      <c r="E15" s="12">
+        <v>46304</v>
+      </c>
+      <c r="F15" s="12">
+        <v>46300</v>
+      </c>
+      <c r="G15" s="12">
+        <v>46304</v>
+      </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
@@ -11845,11 +11901,21 @@
         <v>71</v>
       </c>
       <c r="B16" s="10"/>
-      <c r="C16" s="105"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
+      <c r="C16" s="105">
+        <v>1</v>
+      </c>
+      <c r="D16" s="12">
+        <v>46291</v>
+      </c>
+      <c r="E16" s="12">
+        <v>46293</v>
+      </c>
+      <c r="F16" s="12">
+        <v>46291</v>
+      </c>
+      <c r="G16" s="12">
+        <v>46293</v>
+      </c>
       <c r="H16" s="13"/>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
@@ -11937,7 +12003,9 @@
       <c r="CN16" s="15"/>
     </row>
     <row r="17" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A17" s="99"/>
+      <c r="A17" s="99" t="s">
+        <v>95</v>
+      </c>
       <c r="B17" s="10"/>
       <c r="C17" s="105"/>
       <c r="D17" s="12"/>
@@ -12225,11 +12293,21 @@
         <v>78</v>
       </c>
       <c r="B20" s="23"/>
-      <c r="C20" s="106"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
+      <c r="C20" s="106">
+        <v>1</v>
+      </c>
+      <c r="D20" s="25">
+        <v>46281</v>
+      </c>
+      <c r="E20" s="25">
+        <v>46283</v>
+      </c>
+      <c r="F20" s="25">
+        <v>46281</v>
+      </c>
+      <c r="G20" s="25">
+        <v>46283</v>
+      </c>
       <c r="H20" s="26"/>
       <c r="I20" s="27"/>
       <c r="J20" s="27"/>
@@ -12801,11 +12879,21 @@
         <v>84</v>
       </c>
       <c r="B26" s="23"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
+      <c r="C26" s="106">
+        <v>1</v>
+      </c>
+      <c r="D26" s="25">
+        <v>46284</v>
+      </c>
+      <c r="E26" s="25">
+        <v>46286</v>
+      </c>
+      <c r="F26" s="25">
+        <v>46284</v>
+      </c>
+      <c r="G26" s="25">
+        <v>46286</v>
+      </c>
       <c r="H26" s="26"/>
       <c r="I26" s="27"/>
       <c r="J26" s="27"/>
@@ -14441,7 +14529,9 @@
         <v>75</v>
       </c>
       <c r="B43" s="94"/>
-      <c r="C43" s="111"/>
+      <c r="C43" s="111">
+        <v>0.8</v>
+      </c>
       <c r="D43" s="90">
         <v>46280</v>
       </c>
@@ -15304,18 +15394,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -15332,6 +15410,18 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="G43:G44 F9:G41">
@@ -15345,33 +15435,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A6A6C361903FA540AF4D79E6EA2B777C" ma:contentTypeVersion="18" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ea7c12cc56e366ff4dda5c6e96eadaab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaa52e1c-8772-4366-aa63-bf636c80ebd4" xmlns:ns3="0c73c1f5-50cd-4477-a315-44bef7b8a847" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7966d967ae6f075ad6e4da9e3740ee6a" ns2:_="" ns3:_="">
     <xsd:import namespace="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
@@ -15626,10 +15689,48 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8D2A65F-21CC-403E-82EF-9B2DA85938F8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15646,20 +15747,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8D2A65F-21CC-403E-82EF-9B2DA85938F8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/資料/ガントチャート_4GA3_遠藤直樹.xlsx
+++ b/資料/ガントチャート_4GA3_遠藤直樹.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16A0477-2C48-445D-A36F-A0D59317C504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF3C53F-5ECE-4E7E-9162-372691F65FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5175" yWindow="3600" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="制作進捗確認表" sheetId="16" state="hidden" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="95">
   <si>
     <t>企画制作　進捗管理表</t>
     <phoneticPr fontId="19"/>
@@ -490,10 +490,6 @@
     <rPh sb="0" eb="3">
       <t>シヨウショ</t>
     </rPh>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
     <phoneticPr fontId="19"/>
   </si>
   <si>
@@ -1865,20 +1861,11 @@
       <alignment horizontal="left" indent="1" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -1900,6 +1887,15 @@
     </xf>
     <xf numFmtId="183" fontId="23" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2491,22 +2487,22 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="118">
+      <c r="E1" s="114">
         <v>45761</v>
       </c>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
     </row>
     <row r="2" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -2514,15 +2510,15 @@
       <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -2530,15 +2526,15 @@
       <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A4" s="119" t="s">
+      <c r="A4" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -2546,10 +2542,10 @@
       <c r="L4" s="83"/>
     </row>
     <row r="5" spans="1:92" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="123"/>
-      <c r="E5" s="123"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
       <c r="AU5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2562,161 +2558,161 @@
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="125"/>
-      <c r="C6" s="125"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="114">
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="115">
         <f>H7</f>
         <v>45761</v>
       </c>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="114"/>
-      <c r="M6" s="114">
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115">
         <f>H6+7</f>
         <v>45768</v>
       </c>
-      <c r="N6" s="114"/>
-      <c r="O6" s="114"/>
-      <c r="P6" s="114"/>
-      <c r="Q6" s="114"/>
-      <c r="R6" s="114">
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="115">
         <f>M6+7</f>
         <v>45775</v>
       </c>
-      <c r="S6" s="114"/>
-      <c r="T6" s="114"/>
-      <c r="U6" s="114"/>
-      <c r="V6" s="114"/>
-      <c r="W6" s="114">
+      <c r="S6" s="115"/>
+      <c r="T6" s="115"/>
+      <c r="U6" s="115"/>
+      <c r="V6" s="115"/>
+      <c r="W6" s="115">
         <f>R6+7</f>
         <v>45782</v>
       </c>
-      <c r="X6" s="114"/>
-      <c r="Y6" s="114"/>
-      <c r="Z6" s="114"/>
-      <c r="AA6" s="114"/>
-      <c r="AB6" s="114">
+      <c r="X6" s="115"/>
+      <c r="Y6" s="115"/>
+      <c r="Z6" s="115"/>
+      <c r="AA6" s="115"/>
+      <c r="AB6" s="115">
         <f>W6+7</f>
         <v>45789</v>
       </c>
-      <c r="AC6" s="114"/>
-      <c r="AD6" s="114"/>
-      <c r="AE6" s="114"/>
-      <c r="AF6" s="114"/>
-      <c r="AG6" s="114">
+      <c r="AC6" s="115"/>
+      <c r="AD6" s="115"/>
+      <c r="AE6" s="115"/>
+      <c r="AF6" s="115"/>
+      <c r="AG6" s="115">
         <f>AB6+7</f>
         <v>45796</v>
       </c>
-      <c r="AH6" s="114"/>
-      <c r="AI6" s="114"/>
-      <c r="AJ6" s="114"/>
-      <c r="AK6" s="114"/>
-      <c r="AL6" s="114">
+      <c r="AH6" s="115"/>
+      <c r="AI6" s="115"/>
+      <c r="AJ6" s="115"/>
+      <c r="AK6" s="115"/>
+      <c r="AL6" s="115">
         <f>AG6+7</f>
         <v>45803</v>
       </c>
-      <c r="AM6" s="114"/>
-      <c r="AN6" s="114"/>
-      <c r="AO6" s="114"/>
-      <c r="AP6" s="114"/>
-      <c r="AQ6" s="114">
+      <c r="AM6" s="115"/>
+      <c r="AN6" s="115"/>
+      <c r="AO6" s="115"/>
+      <c r="AP6" s="115"/>
+      <c r="AQ6" s="115">
         <f>AL6+7</f>
         <v>45810</v>
       </c>
-      <c r="AR6" s="114"/>
-      <c r="AS6" s="114"/>
-      <c r="AT6" s="114"/>
-      <c r="AU6" s="114"/>
-      <c r="AV6" s="114">
+      <c r="AR6" s="115"/>
+      <c r="AS6" s="115"/>
+      <c r="AT6" s="115"/>
+      <c r="AU6" s="115"/>
+      <c r="AV6" s="115">
         <f>AQ6+7</f>
         <v>45817</v>
       </c>
-      <c r="AW6" s="114"/>
-      <c r="AX6" s="114"/>
-      <c r="AY6" s="114"/>
-      <c r="AZ6" s="114"/>
-      <c r="BA6" s="114">
+      <c r="AW6" s="115"/>
+      <c r="AX6" s="115"/>
+      <c r="AY6" s="115"/>
+      <c r="AZ6" s="115"/>
+      <c r="BA6" s="115">
         <f>AV6+7</f>
         <v>45824</v>
       </c>
-      <c r="BB6" s="114"/>
-      <c r="BC6" s="114"/>
-      <c r="BD6" s="114"/>
-      <c r="BE6" s="114"/>
-      <c r="BF6" s="114">
+      <c r="BB6" s="115"/>
+      <c r="BC6" s="115"/>
+      <c r="BD6" s="115"/>
+      <c r="BE6" s="115"/>
+      <c r="BF6" s="115">
         <f>BA6+7</f>
         <v>45831</v>
       </c>
-      <c r="BG6" s="114"/>
-      <c r="BH6" s="114"/>
-      <c r="BI6" s="114"/>
-      <c r="BJ6" s="114"/>
-      <c r="BK6" s="114">
+      <c r="BG6" s="115"/>
+      <c r="BH6" s="115"/>
+      <c r="BI6" s="115"/>
+      <c r="BJ6" s="115"/>
+      <c r="BK6" s="115">
         <f>BF6+7</f>
         <v>45838</v>
       </c>
-      <c r="BL6" s="114"/>
-      <c r="BM6" s="114"/>
-      <c r="BN6" s="114"/>
-      <c r="BO6" s="114"/>
-      <c r="BP6" s="114">
+      <c r="BL6" s="115"/>
+      <c r="BM6" s="115"/>
+      <c r="BN6" s="115"/>
+      <c r="BO6" s="115"/>
+      <c r="BP6" s="115">
         <f>BK6+7</f>
         <v>45845</v>
       </c>
-      <c r="BQ6" s="114"/>
-      <c r="BR6" s="114"/>
-      <c r="BS6" s="114"/>
-      <c r="BT6" s="114"/>
-      <c r="BU6" s="114">
+      <c r="BQ6" s="115"/>
+      <c r="BR6" s="115"/>
+      <c r="BS6" s="115"/>
+      <c r="BT6" s="115"/>
+      <c r="BU6" s="115">
         <f>BP6+7</f>
         <v>45852</v>
       </c>
-      <c r="BV6" s="114"/>
-      <c r="BW6" s="114"/>
-      <c r="BX6" s="114"/>
-      <c r="BY6" s="114"/>
-      <c r="BZ6" s="114">
+      <c r="BV6" s="115"/>
+      <c r="BW6" s="115"/>
+      <c r="BX6" s="115"/>
+      <c r="BY6" s="115"/>
+      <c r="BZ6" s="115">
         <f>BU6+7</f>
         <v>45859</v>
       </c>
-      <c r="CA6" s="114"/>
-      <c r="CB6" s="114"/>
-      <c r="CC6" s="114"/>
-      <c r="CD6" s="114"/>
-      <c r="CE6" s="114">
+      <c r="CA6" s="115"/>
+      <c r="CB6" s="115"/>
+      <c r="CC6" s="115"/>
+      <c r="CD6" s="115"/>
+      <c r="CE6" s="115">
         <f>BZ6+7</f>
         <v>45866</v>
       </c>
-      <c r="CF6" s="114"/>
-      <c r="CG6" s="114"/>
-      <c r="CH6" s="114"/>
-      <c r="CI6" s="114"/>
-      <c r="CJ6" s="114">
+      <c r="CF6" s="115"/>
+      <c r="CG6" s="115"/>
+      <c r="CH6" s="115"/>
+      <c r="CI6" s="115"/>
+      <c r="CJ6" s="115">
         <f>CE6+7</f>
         <v>45873</v>
       </c>
-      <c r="CK6" s="114"/>
-      <c r="CL6" s="114"/>
-      <c r="CM6" s="114"/>
-      <c r="CN6" s="114"/>
+      <c r="CK6" s="115"/>
+      <c r="CL6" s="115"/>
+      <c r="CM6" s="115"/>
+      <c r="CN6" s="115"/>
     </row>
     <row r="7" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="115" t="s">
+      <c r="D7" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="116"/>
-      <c r="F7" s="117" t="s">
+      <c r="E7" s="124"/>
+      <c r="F7" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="116"/>
+      <c r="G7" s="124"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>45761</v>
@@ -6040,18 +6036,6 @@
   </sheetData>
   <sheetProtection password="DF87" sheet="1" insertRows="0"/>
   <mergeCells count="28">
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="AG6:AK6"/>
-    <mergeCell ref="AL6:AP6"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
     <mergeCell ref="BU6:BY6"/>
     <mergeCell ref="BZ6:CD6"/>
     <mergeCell ref="CE6:CI6"/>
@@ -6068,6 +6052,18 @@
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB6:AF6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="AG6:AK6"/>
+    <mergeCell ref="AL6:AP6"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G34">
@@ -6136,22 +6132,22 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="118">
+      <c r="E1" s="114">
         <v>45761</v>
       </c>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
     </row>
     <row r="2" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -6159,15 +6155,15 @@
       <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -6175,15 +6171,15 @@
       <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="119" t="s">
+      <c r="A4" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -6191,10 +6187,10 @@
       <c r="L4" s="83"/>
     </row>
     <row r="5" spans="1:92" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="123"/>
-      <c r="E5" s="123"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
       <c r="AU5" s="1" t="s">
         <v>5</v>
       </c>
@@ -6207,161 +6203,161 @@
     </row>
     <row r="6" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="125"/>
-      <c r="C6" s="125"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="114">
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="115">
         <f>H7</f>
         <v>45761</v>
       </c>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="114"/>
-      <c r="M6" s="114">
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115">
         <f>H6+7</f>
         <v>45768</v>
       </c>
-      <c r="N6" s="114"/>
-      <c r="O6" s="114"/>
-      <c r="P6" s="114"/>
-      <c r="Q6" s="114"/>
-      <c r="R6" s="114">
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="115">
         <f>M6+7</f>
         <v>45775</v>
       </c>
-      <c r="S6" s="114"/>
-      <c r="T6" s="114"/>
-      <c r="U6" s="114"/>
-      <c r="V6" s="114"/>
-      <c r="W6" s="114">
+      <c r="S6" s="115"/>
+      <c r="T6" s="115"/>
+      <c r="U6" s="115"/>
+      <c r="V6" s="115"/>
+      <c r="W6" s="115">
         <f>R6+7</f>
         <v>45782</v>
       </c>
-      <c r="X6" s="114"/>
-      <c r="Y6" s="114"/>
-      <c r="Z6" s="114"/>
-      <c r="AA6" s="114"/>
-      <c r="AB6" s="114">
+      <c r="X6" s="115"/>
+      <c r="Y6" s="115"/>
+      <c r="Z6" s="115"/>
+      <c r="AA6" s="115"/>
+      <c r="AB6" s="115">
         <f>W6+7</f>
         <v>45789</v>
       </c>
-      <c r="AC6" s="114"/>
-      <c r="AD6" s="114"/>
-      <c r="AE6" s="114"/>
-      <c r="AF6" s="114"/>
-      <c r="AG6" s="114">
+      <c r="AC6" s="115"/>
+      <c r="AD6" s="115"/>
+      <c r="AE6" s="115"/>
+      <c r="AF6" s="115"/>
+      <c r="AG6" s="115">
         <f>AB6+7</f>
         <v>45796</v>
       </c>
-      <c r="AH6" s="114"/>
-      <c r="AI6" s="114"/>
-      <c r="AJ6" s="114"/>
-      <c r="AK6" s="114"/>
-      <c r="AL6" s="114">
+      <c r="AH6" s="115"/>
+      <c r="AI6" s="115"/>
+      <c r="AJ6" s="115"/>
+      <c r="AK6" s="115"/>
+      <c r="AL6" s="115">
         <f>AG6+7</f>
         <v>45803</v>
       </c>
-      <c r="AM6" s="114"/>
-      <c r="AN6" s="114"/>
-      <c r="AO6" s="114"/>
-      <c r="AP6" s="114"/>
-      <c r="AQ6" s="114">
+      <c r="AM6" s="115"/>
+      <c r="AN6" s="115"/>
+      <c r="AO6" s="115"/>
+      <c r="AP6" s="115"/>
+      <c r="AQ6" s="115">
         <f>AL6+7</f>
         <v>45810</v>
       </c>
-      <c r="AR6" s="114"/>
-      <c r="AS6" s="114"/>
-      <c r="AT6" s="114"/>
-      <c r="AU6" s="114"/>
-      <c r="AV6" s="114">
+      <c r="AR6" s="115"/>
+      <c r="AS6" s="115"/>
+      <c r="AT6" s="115"/>
+      <c r="AU6" s="115"/>
+      <c r="AV6" s="115">
         <f>AQ6+7</f>
         <v>45817</v>
       </c>
-      <c r="AW6" s="114"/>
-      <c r="AX6" s="114"/>
-      <c r="AY6" s="114"/>
-      <c r="AZ6" s="114"/>
-      <c r="BA6" s="114">
+      <c r="AW6" s="115"/>
+      <c r="AX6" s="115"/>
+      <c r="AY6" s="115"/>
+      <c r="AZ6" s="115"/>
+      <c r="BA6" s="115">
         <f>AV6+7</f>
         <v>45824</v>
       </c>
-      <c r="BB6" s="114"/>
-      <c r="BC6" s="114"/>
-      <c r="BD6" s="114"/>
-      <c r="BE6" s="114"/>
-      <c r="BF6" s="114">
+      <c r="BB6" s="115"/>
+      <c r="BC6" s="115"/>
+      <c r="BD6" s="115"/>
+      <c r="BE6" s="115"/>
+      <c r="BF6" s="115">
         <f>BA6+7</f>
         <v>45831</v>
       </c>
-      <c r="BG6" s="114"/>
-      <c r="BH6" s="114"/>
-      <c r="BI6" s="114"/>
-      <c r="BJ6" s="114"/>
-      <c r="BK6" s="114">
+      <c r="BG6" s="115"/>
+      <c r="BH6" s="115"/>
+      <c r="BI6" s="115"/>
+      <c r="BJ6" s="115"/>
+      <c r="BK6" s="115">
         <f>BF6+7</f>
         <v>45838</v>
       </c>
-      <c r="BL6" s="114"/>
-      <c r="BM6" s="114"/>
-      <c r="BN6" s="114"/>
-      <c r="BO6" s="114"/>
-      <c r="BP6" s="114">
+      <c r="BL6" s="115"/>
+      <c r="BM6" s="115"/>
+      <c r="BN6" s="115"/>
+      <c r="BO6" s="115"/>
+      <c r="BP6" s="115">
         <f>BK6+7</f>
         <v>45845</v>
       </c>
-      <c r="BQ6" s="114"/>
-      <c r="BR6" s="114"/>
-      <c r="BS6" s="114"/>
-      <c r="BT6" s="114"/>
-      <c r="BU6" s="114">
+      <c r="BQ6" s="115"/>
+      <c r="BR6" s="115"/>
+      <c r="BS6" s="115"/>
+      <c r="BT6" s="115"/>
+      <c r="BU6" s="115">
         <f>BP6+7</f>
         <v>45852</v>
       </c>
-      <c r="BV6" s="114"/>
-      <c r="BW6" s="114"/>
-      <c r="BX6" s="114"/>
-      <c r="BY6" s="114"/>
-      <c r="BZ6" s="114">
+      <c r="BV6" s="115"/>
+      <c r="BW6" s="115"/>
+      <c r="BX6" s="115"/>
+      <c r="BY6" s="115"/>
+      <c r="BZ6" s="115">
         <f>BU6+7</f>
         <v>45859</v>
       </c>
-      <c r="CA6" s="114"/>
-      <c r="CB6" s="114"/>
-      <c r="CC6" s="114"/>
-      <c r="CD6" s="114"/>
-      <c r="CE6" s="114">
+      <c r="CA6" s="115"/>
+      <c r="CB6" s="115"/>
+      <c r="CC6" s="115"/>
+      <c r="CD6" s="115"/>
+      <c r="CE6" s="115">
         <f>BZ6+7</f>
         <v>45866</v>
       </c>
-      <c r="CF6" s="114"/>
-      <c r="CG6" s="114"/>
-      <c r="CH6" s="114"/>
-      <c r="CI6" s="114"/>
-      <c r="CJ6" s="114">
+      <c r="CF6" s="115"/>
+      <c r="CG6" s="115"/>
+      <c r="CH6" s="115"/>
+      <c r="CI6" s="115"/>
+      <c r="CJ6" s="115">
         <f>CE6+7</f>
         <v>45873</v>
       </c>
-      <c r="CK6" s="114"/>
-      <c r="CL6" s="114"/>
-      <c r="CM6" s="114"/>
-      <c r="CN6" s="114"/>
+      <c r="CK6" s="115"/>
+      <c r="CL6" s="115"/>
+      <c r="CM6" s="115"/>
+      <c r="CN6" s="115"/>
     </row>
     <row r="7" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="115" t="s">
+      <c r="D7" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="116"/>
-      <c r="F7" s="117" t="s">
+      <c r="E7" s="124"/>
+      <c r="F7" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="116"/>
+      <c r="G7" s="124"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>45761</v>
@@ -9858,6 +9854,18 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="28">
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -9874,18 +9882,6 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G35">
@@ -9917,11 +9913,11 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="118">
+      <c r="E1" s="114">
         <v>46280</v>
       </c>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -10009,15 +10005,15 @@
       <c r="CN1" s="1"/>
     </row>
     <row r="2" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A2" s="119" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
+      <c r="A2" s="116" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -10105,15 +10101,15 @@
       <c r="CN2" s="1"/>
     </row>
     <row r="3" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -10201,15 +10197,15 @@
       <c r="CN3" s="1"/>
     </row>
     <row r="4" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A4" s="119" t="s">
+      <c r="A4" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -10300,10 +10296,10 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="123"/>
-      <c r="E5" s="123"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -10398,161 +10394,161 @@
     </row>
     <row r="6" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="125"/>
-      <c r="C6" s="125"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="114">
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="115">
         <f>H7</f>
         <v>46279</v>
       </c>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="114"/>
-      <c r="M6" s="114">
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115">
         <f>H6+7</f>
         <v>46286</v>
       </c>
-      <c r="N6" s="114"/>
-      <c r="O6" s="114"/>
-      <c r="P6" s="114"/>
-      <c r="Q6" s="114"/>
-      <c r="R6" s="114">
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="115">
         <f>M6+7</f>
         <v>46293</v>
       </c>
-      <c r="S6" s="114"/>
-      <c r="T6" s="114"/>
-      <c r="U6" s="114"/>
-      <c r="V6" s="114"/>
-      <c r="W6" s="114">
+      <c r="S6" s="115"/>
+      <c r="T6" s="115"/>
+      <c r="U6" s="115"/>
+      <c r="V6" s="115"/>
+      <c r="W6" s="115">
         <f>R6+7</f>
         <v>46300</v>
       </c>
-      <c r="X6" s="114"/>
-      <c r="Y6" s="114"/>
-      <c r="Z6" s="114"/>
-      <c r="AA6" s="114"/>
-      <c r="AB6" s="114">
+      <c r="X6" s="115"/>
+      <c r="Y6" s="115"/>
+      <c r="Z6" s="115"/>
+      <c r="AA6" s="115"/>
+      <c r="AB6" s="115">
         <f>W6+7</f>
         <v>46307</v>
       </c>
-      <c r="AC6" s="114"/>
-      <c r="AD6" s="114"/>
-      <c r="AE6" s="114"/>
-      <c r="AF6" s="114"/>
-      <c r="AG6" s="114">
+      <c r="AC6" s="115"/>
+      <c r="AD6" s="115"/>
+      <c r="AE6" s="115"/>
+      <c r="AF6" s="115"/>
+      <c r="AG6" s="115">
         <f>AB6+7</f>
         <v>46314</v>
       </c>
-      <c r="AH6" s="114"/>
-      <c r="AI6" s="114"/>
-      <c r="AJ6" s="114"/>
-      <c r="AK6" s="114"/>
-      <c r="AL6" s="114">
+      <c r="AH6" s="115"/>
+      <c r="AI6" s="115"/>
+      <c r="AJ6" s="115"/>
+      <c r="AK6" s="115"/>
+      <c r="AL6" s="115">
         <f>AG6+7</f>
         <v>46321</v>
       </c>
-      <c r="AM6" s="114"/>
-      <c r="AN6" s="114"/>
-      <c r="AO6" s="114"/>
-      <c r="AP6" s="114"/>
-      <c r="AQ6" s="114">
+      <c r="AM6" s="115"/>
+      <c r="AN6" s="115"/>
+      <c r="AO6" s="115"/>
+      <c r="AP6" s="115"/>
+      <c r="AQ6" s="115">
         <f>AL6+7</f>
         <v>46328</v>
       </c>
-      <c r="AR6" s="114"/>
-      <c r="AS6" s="114"/>
-      <c r="AT6" s="114"/>
-      <c r="AU6" s="114"/>
-      <c r="AV6" s="114">
+      <c r="AR6" s="115"/>
+      <c r="AS6" s="115"/>
+      <c r="AT6" s="115"/>
+      <c r="AU6" s="115"/>
+      <c r="AV6" s="115">
         <f>AQ6+7</f>
         <v>46335</v>
       </c>
-      <c r="AW6" s="114"/>
-      <c r="AX6" s="114"/>
-      <c r="AY6" s="114"/>
-      <c r="AZ6" s="114"/>
-      <c r="BA6" s="114">
+      <c r="AW6" s="115"/>
+      <c r="AX6" s="115"/>
+      <c r="AY6" s="115"/>
+      <c r="AZ6" s="115"/>
+      <c r="BA6" s="115">
         <f>AV6+7</f>
         <v>46342</v>
       </c>
-      <c r="BB6" s="114"/>
-      <c r="BC6" s="114"/>
-      <c r="BD6" s="114"/>
-      <c r="BE6" s="114"/>
-      <c r="BF6" s="114">
+      <c r="BB6" s="115"/>
+      <c r="BC6" s="115"/>
+      <c r="BD6" s="115"/>
+      <c r="BE6" s="115"/>
+      <c r="BF6" s="115">
         <f>BA6+7</f>
         <v>46349</v>
       </c>
-      <c r="BG6" s="114"/>
-      <c r="BH6" s="114"/>
-      <c r="BI6" s="114"/>
-      <c r="BJ6" s="114"/>
-      <c r="BK6" s="114">
+      <c r="BG6" s="115"/>
+      <c r="BH6" s="115"/>
+      <c r="BI6" s="115"/>
+      <c r="BJ6" s="115"/>
+      <c r="BK6" s="115">
         <f>BF6+7</f>
         <v>46356</v>
       </c>
-      <c r="BL6" s="114"/>
-      <c r="BM6" s="114"/>
-      <c r="BN6" s="114"/>
-      <c r="BO6" s="114"/>
-      <c r="BP6" s="114">
+      <c r="BL6" s="115"/>
+      <c r="BM6" s="115"/>
+      <c r="BN6" s="115"/>
+      <c r="BO6" s="115"/>
+      <c r="BP6" s="115">
         <f>BK6+7</f>
         <v>46363</v>
       </c>
-      <c r="BQ6" s="114"/>
-      <c r="BR6" s="114"/>
-      <c r="BS6" s="114"/>
-      <c r="BT6" s="114"/>
-      <c r="BU6" s="114">
+      <c r="BQ6" s="115"/>
+      <c r="BR6" s="115"/>
+      <c r="BS6" s="115"/>
+      <c r="BT6" s="115"/>
+      <c r="BU6" s="115">
         <f>BP6+7</f>
         <v>46370</v>
       </c>
-      <c r="BV6" s="114"/>
-      <c r="BW6" s="114"/>
-      <c r="BX6" s="114"/>
-      <c r="BY6" s="114"/>
-      <c r="BZ6" s="114">
+      <c r="BV6" s="115"/>
+      <c r="BW6" s="115"/>
+      <c r="BX6" s="115"/>
+      <c r="BY6" s="115"/>
+      <c r="BZ6" s="115">
         <f>BU6+7</f>
         <v>46377</v>
       </c>
-      <c r="CA6" s="114"/>
-      <c r="CB6" s="114"/>
-      <c r="CC6" s="114"/>
-      <c r="CD6" s="114"/>
-      <c r="CE6" s="114">
+      <c r="CA6" s="115"/>
+      <c r="CB6" s="115"/>
+      <c r="CC6" s="115"/>
+      <c r="CD6" s="115"/>
+      <c r="CE6" s="115">
         <f>BZ6+7</f>
         <v>46384</v>
       </c>
-      <c r="CF6" s="114"/>
-      <c r="CG6" s="114"/>
-      <c r="CH6" s="114"/>
-      <c r="CI6" s="114"/>
-      <c r="CJ6" s="114">
+      <c r="CF6" s="115"/>
+      <c r="CG6" s="115"/>
+      <c r="CH6" s="115"/>
+      <c r="CI6" s="115"/>
+      <c r="CJ6" s="115">
         <f>CE6+7</f>
         <v>46391</v>
       </c>
-      <c r="CK6" s="114"/>
-      <c r="CL6" s="114"/>
-      <c r="CM6" s="114"/>
-      <c r="CN6" s="114"/>
+      <c r="CK6" s="115"/>
+      <c r="CL6" s="115"/>
+      <c r="CM6" s="115"/>
+      <c r="CN6" s="115"/>
     </row>
     <row r="7" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="115" t="s">
+      <c r="D7" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="116"/>
-      <c r="F7" s="117" t="s">
+      <c r="E7" s="124"/>
+      <c r="F7" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="116"/>
+      <c r="G7" s="124"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>46279</v>
@@ -11492,7 +11488,9 @@
       <c r="E12" s="12">
         <v>46315</v>
       </c>
-      <c r="F12" s="12"/>
+      <c r="F12" s="12">
+        <v>46306</v>
+      </c>
       <c r="G12" s="12"/>
       <c r="H12" s="13"/>
       <c r="I12" s="14"/>
@@ -12004,7 +12002,7 @@
     </row>
     <row r="17" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A17" s="99" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="105"/>
@@ -12290,7 +12288,7 @@
     </row>
     <row r="20" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A20" s="113" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20" s="23"/>
       <c r="C20" s="106">
@@ -12396,13 +12394,21 @@
     </row>
     <row r="21" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A21" s="100" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="23"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
+      <c r="C21" s="106">
+        <v>0</v>
+      </c>
+      <c r="D21" s="25">
+        <v>46318</v>
+      </c>
+      <c r="E21" s="25">
+        <v>46320</v>
+      </c>
+      <c r="F21" s="25">
+        <v>46318</v>
+      </c>
       <c r="G21" s="25"/>
       <c r="H21" s="26"/>
       <c r="I21" s="27"/>
@@ -12492,13 +12498,21 @@
     </row>
     <row r="22" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A22" s="113" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B22" s="23"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
+      <c r="C22" s="106">
+        <v>0.05</v>
+      </c>
+      <c r="D22" s="25">
+        <v>46281</v>
+      </c>
+      <c r="E22" s="25">
+        <v>46346</v>
+      </c>
+      <c r="F22" s="25">
+        <v>46281</v>
+      </c>
       <c r="G22" s="25"/>
       <c r="H22" s="26"/>
       <c r="I22" s="27"/>
@@ -12588,13 +12602,21 @@
     </row>
     <row r="23" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A23" s="100" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B23" s="23"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
+      <c r="C23" s="106">
+        <v>0.05</v>
+      </c>
+      <c r="D23" s="25">
+        <v>46281</v>
+      </c>
+      <c r="E23" s="25">
+        <v>46346</v>
+      </c>
+      <c r="F23" s="25">
+        <v>46281</v>
+      </c>
       <c r="G23" s="25"/>
       <c r="H23" s="26"/>
       <c r="I23" s="27"/>
@@ -12684,13 +12706,21 @@
     </row>
     <row r="24" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A24" s="100" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B24" s="23"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
+      <c r="C24" s="106">
+        <v>0.05</v>
+      </c>
+      <c r="D24" s="25">
+        <v>46281</v>
+      </c>
+      <c r="E24" s="25">
+        <v>46346</v>
+      </c>
+      <c r="F24" s="25">
+        <v>46281</v>
+      </c>
       <c r="G24" s="25"/>
       <c r="H24" s="26"/>
       <c r="I24" s="27"/>
@@ -12780,13 +12810,21 @@
     </row>
     <row r="25" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A25" s="113" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B25" s="23"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
+      <c r="C25" s="106">
+        <v>0.5</v>
+      </c>
+      <c r="D25" s="25">
+        <v>46284</v>
+      </c>
+      <c r="E25" s="25">
+        <v>46317</v>
+      </c>
+      <c r="F25" s="25">
+        <v>46284</v>
+      </c>
       <c r="G25" s="25"/>
       <c r="H25" s="26"/>
       <c r="I25" s="27"/>
@@ -12876,7 +12914,7 @@
     </row>
     <row r="26" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A26" s="100" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B26" s="23"/>
       <c r="C26" s="106">
@@ -12982,13 +13020,21 @@
     </row>
     <row r="27" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A27" s="100" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B27" s="23"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
+      <c r="C27" s="106">
+        <v>0.3</v>
+      </c>
+      <c r="D27" s="25">
+        <v>46308</v>
+      </c>
+      <c r="E27" s="25">
+        <v>46317</v>
+      </c>
+      <c r="F27" s="25">
+        <v>46308</v>
+      </c>
       <c r="G27" s="25"/>
       <c r="H27" s="26"/>
       <c r="I27" s="27"/>
@@ -13078,15 +13124,21 @@
     </row>
     <row r="28" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A28" s="100" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" s="23"/>
-      <c r="C28" s="106" t="s">
-        <v>77</v>
-      </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
+      <c r="C28" s="106">
+        <v>0.3</v>
+      </c>
+      <c r="D28" s="25">
+        <v>46308</v>
+      </c>
+      <c r="E28" s="25">
+        <v>46317</v>
+      </c>
+      <c r="F28" s="25">
+        <v>46308</v>
+      </c>
       <c r="G28" s="25"/>
       <c r="H28" s="26"/>
       <c r="I28" s="27"/>
@@ -13176,13 +13228,21 @@
     </row>
     <row r="29" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A29" s="100" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B29" s="23"/>
-      <c r="C29" s="106"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
+      <c r="C29" s="106">
+        <v>0.3</v>
+      </c>
+      <c r="D29" s="25">
+        <v>46308</v>
+      </c>
+      <c r="E29" s="25">
+        <v>46317</v>
+      </c>
+      <c r="F29" s="25">
+        <v>46308</v>
+      </c>
       <c r="G29" s="25"/>
       <c r="H29" s="26"/>
       <c r="I29" s="27"/>
@@ -13272,12 +13332,18 @@
     </row>
     <row r="30" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A30" s="113" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B30" s="23"/>
-      <c r="C30" s="106"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
+      <c r="C30" s="106">
+        <v>0</v>
+      </c>
+      <c r="D30" s="25">
+        <v>46321</v>
+      </c>
+      <c r="E30" s="25">
+        <v>46346</v>
+      </c>
       <c r="F30" s="25"/>
       <c r="G30" s="25"/>
       <c r="H30" s="26"/>
@@ -13368,12 +13434,18 @@
     </row>
     <row r="31" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A31" s="100" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B31" s="23"/>
-      <c r="C31" s="106"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
+      <c r="C31" s="106">
+        <v>0</v>
+      </c>
+      <c r="D31" s="25">
+        <v>46321</v>
+      </c>
+      <c r="E31" s="25">
+        <v>46328</v>
+      </c>
       <c r="F31" s="25"/>
       <c r="G31" s="25"/>
       <c r="H31" s="26"/>
@@ -13464,12 +13536,18 @@
     </row>
     <row r="32" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A32" s="100" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B32" s="23"/>
-      <c r="C32" s="106"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
+      <c r="C32" s="106">
+        <v>0</v>
+      </c>
+      <c r="D32" s="25">
+        <v>46341</v>
+      </c>
+      <c r="E32" s="25">
+        <v>46344</v>
+      </c>
       <c r="F32" s="25"/>
       <c r="G32" s="25"/>
       <c r="H32" s="26"/>
@@ -13560,12 +13638,18 @@
     </row>
     <row r="33" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A33" s="100" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B33" s="23"/>
-      <c r="C33" s="106"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
+      <c r="C33" s="106">
+        <v>0</v>
+      </c>
+      <c r="D33" s="25">
+        <v>46344</v>
+      </c>
+      <c r="E33" s="25">
+        <v>46346</v>
+      </c>
       <c r="F33" s="25"/>
       <c r="G33" s="25"/>
       <c r="H33" s="26"/>
@@ -13656,12 +13740,18 @@
     </row>
     <row r="34" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A34" s="113" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B34" s="23"/>
-      <c r="C34" s="106"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
+      <c r="C34" s="106">
+        <v>0</v>
+      </c>
+      <c r="D34" s="25">
+        <v>46347</v>
+      </c>
+      <c r="E34" s="25">
+        <v>46351</v>
+      </c>
       <c r="F34" s="25"/>
       <c r="G34" s="25"/>
       <c r="H34" s="26"/>
@@ -13752,12 +13842,18 @@
     </row>
     <row r="35" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A35" s="100" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B35" s="23"/>
-      <c r="C35" s="106"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
+      <c r="C35" s="106">
+        <v>0</v>
+      </c>
+      <c r="D35" s="25">
+        <v>46347</v>
+      </c>
+      <c r="E35" s="25">
+        <v>46351</v>
+      </c>
       <c r="F35" s="25"/>
       <c r="G35" s="25"/>
       <c r="H35" s="26"/>
@@ -14530,7 +14626,7 @@
       </c>
       <c r="B43" s="94"/>
       <c r="C43" s="111">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D43" s="90">
         <v>46280</v>
@@ -14541,7 +14637,9 @@
       <c r="F43" s="90">
         <v>46284</v>
       </c>
-      <c r="G43" s="87"/>
+      <c r="G43" s="87">
+        <v>46290</v>
+      </c>
       <c r="H43" s="86"/>
       <c r="I43" s="86"/>
       <c r="J43" s="86"/>
@@ -15394,6 +15492,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -15410,18 +15520,6 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="G43:G44 F9:G41">
@@ -15690,6 +15788,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
@@ -15705,15 +15812,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15736,6 +15834,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -15744,12 +15850,4 @@
     <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/資料/ガントチャート_4GA3_遠藤直樹.xlsx
+++ b/資料/ガントチャート_4GA3_遠藤直樹.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF3C53F-5ECE-4E7E-9162-372691F65FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B04CC0-DB5C-422E-89B9-F64331669267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24315" yWindow="2670" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="制作進捗確認表" sheetId="16" state="hidden" r:id="rId1"/>
@@ -37,9 +37,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1861,14 +1858,23 @@
       <alignment horizontal="left" indent="1" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="23" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1878,15 +1884,6 @@
     </xf>
     <xf numFmtId="182" fontId="1" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="23" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2487,11 +2484,11 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="114">
+      <c r="E1" s="115">
         <v>45761</v>
       </c>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
     </row>
     <row r="2" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A2" s="116" t="s">
@@ -2542,10 +2539,10 @@
       <c r="L4" s="83"/>
     </row>
     <row r="5" spans="1:92" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
       <c r="AU5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2558,148 +2555,148 @@
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="115">
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="114">
         <f>H7</f>
         <v>45761</v>
       </c>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="115">
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
+      <c r="M6" s="114">
         <f>H6+7</f>
         <v>45768</v>
       </c>
-      <c r="N6" s="115"/>
-      <c r="O6" s="115"/>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="115"/>
-      <c r="R6" s="115">
+      <c r="N6" s="114"/>
+      <c r="O6" s="114"/>
+      <c r="P6" s="114"/>
+      <c r="Q6" s="114"/>
+      <c r="R6" s="114">
         <f>M6+7</f>
         <v>45775</v>
       </c>
-      <c r="S6" s="115"/>
-      <c r="T6" s="115"/>
-      <c r="U6" s="115"/>
-      <c r="V6" s="115"/>
-      <c r="W6" s="115">
+      <c r="S6" s="114"/>
+      <c r="T6" s="114"/>
+      <c r="U6" s="114"/>
+      <c r="V6" s="114"/>
+      <c r="W6" s="114">
         <f>R6+7</f>
         <v>45782</v>
       </c>
-      <c r="X6" s="115"/>
-      <c r="Y6" s="115"/>
-      <c r="Z6" s="115"/>
-      <c r="AA6" s="115"/>
-      <c r="AB6" s="115">
+      <c r="X6" s="114"/>
+      <c r="Y6" s="114"/>
+      <c r="Z6" s="114"/>
+      <c r="AA6" s="114"/>
+      <c r="AB6" s="114">
         <f>W6+7</f>
         <v>45789</v>
       </c>
-      <c r="AC6" s="115"/>
-      <c r="AD6" s="115"/>
-      <c r="AE6" s="115"/>
-      <c r="AF6" s="115"/>
-      <c r="AG6" s="115">
+      <c r="AC6" s="114"/>
+      <c r="AD6" s="114"/>
+      <c r="AE6" s="114"/>
+      <c r="AF6" s="114"/>
+      <c r="AG6" s="114">
         <f>AB6+7</f>
         <v>45796</v>
       </c>
-      <c r="AH6" s="115"/>
-      <c r="AI6" s="115"/>
-      <c r="AJ6" s="115"/>
-      <c r="AK6" s="115"/>
-      <c r="AL6" s="115">
+      <c r="AH6" s="114"/>
+      <c r="AI6" s="114"/>
+      <c r="AJ6" s="114"/>
+      <c r="AK6" s="114"/>
+      <c r="AL6" s="114">
         <f>AG6+7</f>
         <v>45803</v>
       </c>
-      <c r="AM6" s="115"/>
-      <c r="AN6" s="115"/>
-      <c r="AO6" s="115"/>
-      <c r="AP6" s="115"/>
-      <c r="AQ6" s="115">
+      <c r="AM6" s="114"/>
+      <c r="AN6" s="114"/>
+      <c r="AO6" s="114"/>
+      <c r="AP6" s="114"/>
+      <c r="AQ6" s="114">
         <f>AL6+7</f>
         <v>45810</v>
       </c>
-      <c r="AR6" s="115"/>
-      <c r="AS6" s="115"/>
-      <c r="AT6" s="115"/>
-      <c r="AU6" s="115"/>
-      <c r="AV6" s="115">
+      <c r="AR6" s="114"/>
+      <c r="AS6" s="114"/>
+      <c r="AT6" s="114"/>
+      <c r="AU6" s="114"/>
+      <c r="AV6" s="114">
         <f>AQ6+7</f>
         <v>45817</v>
       </c>
-      <c r="AW6" s="115"/>
-      <c r="AX6" s="115"/>
-      <c r="AY6" s="115"/>
-      <c r="AZ6" s="115"/>
-      <c r="BA6" s="115">
+      <c r="AW6" s="114"/>
+      <c r="AX6" s="114"/>
+      <c r="AY6" s="114"/>
+      <c r="AZ6" s="114"/>
+      <c r="BA6" s="114">
         <f>AV6+7</f>
         <v>45824</v>
       </c>
-      <c r="BB6" s="115"/>
-      <c r="BC6" s="115"/>
-      <c r="BD6" s="115"/>
-      <c r="BE6" s="115"/>
-      <c r="BF6" s="115">
+      <c r="BB6" s="114"/>
+      <c r="BC6" s="114"/>
+      <c r="BD6" s="114"/>
+      <c r="BE6" s="114"/>
+      <c r="BF6" s="114">
         <f>BA6+7</f>
         <v>45831</v>
       </c>
-      <c r="BG6" s="115"/>
-      <c r="BH6" s="115"/>
-      <c r="BI6" s="115"/>
-      <c r="BJ6" s="115"/>
-      <c r="BK6" s="115">
+      <c r="BG6" s="114"/>
+      <c r="BH6" s="114"/>
+      <c r="BI6" s="114"/>
+      <c r="BJ6" s="114"/>
+      <c r="BK6" s="114">
         <f>BF6+7</f>
         <v>45838</v>
       </c>
-      <c r="BL6" s="115"/>
-      <c r="BM6" s="115"/>
-      <c r="BN6" s="115"/>
-      <c r="BO6" s="115"/>
-      <c r="BP6" s="115">
+      <c r="BL6" s="114"/>
+      <c r="BM6" s="114"/>
+      <c r="BN6" s="114"/>
+      <c r="BO6" s="114"/>
+      <c r="BP6" s="114">
         <f>BK6+7</f>
         <v>45845</v>
       </c>
-      <c r="BQ6" s="115"/>
-      <c r="BR6" s="115"/>
-      <c r="BS6" s="115"/>
-      <c r="BT6" s="115"/>
-      <c r="BU6" s="115">
+      <c r="BQ6" s="114"/>
+      <c r="BR6" s="114"/>
+      <c r="BS6" s="114"/>
+      <c r="BT6" s="114"/>
+      <c r="BU6" s="114">
         <f>BP6+7</f>
         <v>45852</v>
       </c>
-      <c r="BV6" s="115"/>
-      <c r="BW6" s="115"/>
-      <c r="BX6" s="115"/>
-      <c r="BY6" s="115"/>
-      <c r="BZ6" s="115">
+      <c r="BV6" s="114"/>
+      <c r="BW6" s="114"/>
+      <c r="BX6" s="114"/>
+      <c r="BY6" s="114"/>
+      <c r="BZ6" s="114">
         <f>BU6+7</f>
         <v>45859</v>
       </c>
-      <c r="CA6" s="115"/>
-      <c r="CB6" s="115"/>
-      <c r="CC6" s="115"/>
-      <c r="CD6" s="115"/>
-      <c r="CE6" s="115">
+      <c r="CA6" s="114"/>
+      <c r="CB6" s="114"/>
+      <c r="CC6" s="114"/>
+      <c r="CD6" s="114"/>
+      <c r="CE6" s="114">
         <f>BZ6+7</f>
         <v>45866</v>
       </c>
-      <c r="CF6" s="115"/>
-      <c r="CG6" s="115"/>
-      <c r="CH6" s="115"/>
-      <c r="CI6" s="115"/>
-      <c r="CJ6" s="115">
+      <c r="CF6" s="114"/>
+      <c r="CG6" s="114"/>
+      <c r="CH6" s="114"/>
+      <c r="CI6" s="114"/>
+      <c r="CJ6" s="114">
         <f>CE6+7</f>
         <v>45873</v>
       </c>
-      <c r="CK6" s="115"/>
-      <c r="CL6" s="115"/>
-      <c r="CM6" s="115"/>
-      <c r="CN6" s="115"/>
+      <c r="CK6" s="114"/>
+      <c r="CL6" s="114"/>
+      <c r="CM6" s="114"/>
+      <c r="CN6" s="114"/>
     </row>
     <row r="7" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A7" s="61"/>
@@ -6036,6 +6033,18 @@
   </sheetData>
   <sheetProtection password="DF87" sheet="1" insertRows="0"/>
   <mergeCells count="28">
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="AG6:AK6"/>
+    <mergeCell ref="AL6:AP6"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="BU6:BY6"/>
     <mergeCell ref="BZ6:CD6"/>
     <mergeCell ref="CE6:CI6"/>
@@ -6052,18 +6061,6 @@
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB6:AF6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="AG6:AK6"/>
-    <mergeCell ref="AL6:AP6"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G34">
@@ -6132,11 +6129,11 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="114">
+      <c r="E1" s="115">
         <v>45761</v>
       </c>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
     </row>
     <row r="2" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="116" t="s">
@@ -6187,10 +6184,10 @@
       <c r="L4" s="83"/>
     </row>
     <row r="5" spans="1:92" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
       <c r="AU5" s="1" t="s">
         <v>5</v>
       </c>
@@ -6203,148 +6200,148 @@
     </row>
     <row r="6" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="115">
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="114">
         <f>H7</f>
         <v>45761</v>
       </c>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="115">
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
+      <c r="M6" s="114">
         <f>H6+7</f>
         <v>45768</v>
       </c>
-      <c r="N6" s="115"/>
-      <c r="O6" s="115"/>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="115"/>
-      <c r="R6" s="115">
+      <c r="N6" s="114"/>
+      <c r="O6" s="114"/>
+      <c r="P6" s="114"/>
+      <c r="Q6" s="114"/>
+      <c r="R6" s="114">
         <f>M6+7</f>
         <v>45775</v>
       </c>
-      <c r="S6" s="115"/>
-      <c r="T6" s="115"/>
-      <c r="U6" s="115"/>
-      <c r="V6" s="115"/>
-      <c r="W6" s="115">
+      <c r="S6" s="114"/>
+      <c r="T6" s="114"/>
+      <c r="U6" s="114"/>
+      <c r="V6" s="114"/>
+      <c r="W6" s="114">
         <f>R6+7</f>
         <v>45782</v>
       </c>
-      <c r="X6" s="115"/>
-      <c r="Y6" s="115"/>
-      <c r="Z6" s="115"/>
-      <c r="AA6" s="115"/>
-      <c r="AB6" s="115">
+      <c r="X6" s="114"/>
+      <c r="Y6" s="114"/>
+      <c r="Z6" s="114"/>
+      <c r="AA6" s="114"/>
+      <c r="AB6" s="114">
         <f>W6+7</f>
         <v>45789</v>
       </c>
-      <c r="AC6" s="115"/>
-      <c r="AD6" s="115"/>
-      <c r="AE6" s="115"/>
-      <c r="AF6" s="115"/>
-      <c r="AG6" s="115">
+      <c r="AC6" s="114"/>
+      <c r="AD6" s="114"/>
+      <c r="AE6" s="114"/>
+      <c r="AF6" s="114"/>
+      <c r="AG6" s="114">
         <f>AB6+7</f>
         <v>45796</v>
       </c>
-      <c r="AH6" s="115"/>
-      <c r="AI6" s="115"/>
-      <c r="AJ6" s="115"/>
-      <c r="AK6" s="115"/>
-      <c r="AL6" s="115">
+      <c r="AH6" s="114"/>
+      <c r="AI6" s="114"/>
+      <c r="AJ6" s="114"/>
+      <c r="AK6" s="114"/>
+      <c r="AL6" s="114">
         <f>AG6+7</f>
         <v>45803</v>
       </c>
-      <c r="AM6" s="115"/>
-      <c r="AN6" s="115"/>
-      <c r="AO6" s="115"/>
-      <c r="AP6" s="115"/>
-      <c r="AQ6" s="115">
+      <c r="AM6" s="114"/>
+      <c r="AN6" s="114"/>
+      <c r="AO6" s="114"/>
+      <c r="AP6" s="114"/>
+      <c r="AQ6" s="114">
         <f>AL6+7</f>
         <v>45810</v>
       </c>
-      <c r="AR6" s="115"/>
-      <c r="AS6" s="115"/>
-      <c r="AT6" s="115"/>
-      <c r="AU6" s="115"/>
-      <c r="AV6" s="115">
+      <c r="AR6" s="114"/>
+      <c r="AS6" s="114"/>
+      <c r="AT6" s="114"/>
+      <c r="AU6" s="114"/>
+      <c r="AV6" s="114">
         <f>AQ6+7</f>
         <v>45817</v>
       </c>
-      <c r="AW6" s="115"/>
-      <c r="AX6" s="115"/>
-      <c r="AY6" s="115"/>
-      <c r="AZ6" s="115"/>
-      <c r="BA6" s="115">
+      <c r="AW6" s="114"/>
+      <c r="AX6" s="114"/>
+      <c r="AY6" s="114"/>
+      <c r="AZ6" s="114"/>
+      <c r="BA6" s="114">
         <f>AV6+7</f>
         <v>45824</v>
       </c>
-      <c r="BB6" s="115"/>
-      <c r="BC6" s="115"/>
-      <c r="BD6" s="115"/>
-      <c r="BE6" s="115"/>
-      <c r="BF6" s="115">
+      <c r="BB6" s="114"/>
+      <c r="BC6" s="114"/>
+      <c r="BD6" s="114"/>
+      <c r="BE6" s="114"/>
+      <c r="BF6" s="114">
         <f>BA6+7</f>
         <v>45831</v>
       </c>
-      <c r="BG6" s="115"/>
-      <c r="BH6" s="115"/>
-      <c r="BI6" s="115"/>
-      <c r="BJ6" s="115"/>
-      <c r="BK6" s="115">
+      <c r="BG6" s="114"/>
+      <c r="BH6" s="114"/>
+      <c r="BI6" s="114"/>
+      <c r="BJ6" s="114"/>
+      <c r="BK6" s="114">
         <f>BF6+7</f>
         <v>45838</v>
       </c>
-      <c r="BL6" s="115"/>
-      <c r="BM6" s="115"/>
-      <c r="BN6" s="115"/>
-      <c r="BO6" s="115"/>
-      <c r="BP6" s="115">
+      <c r="BL6" s="114"/>
+      <c r="BM6" s="114"/>
+      <c r="BN6" s="114"/>
+      <c r="BO6" s="114"/>
+      <c r="BP6" s="114">
         <f>BK6+7</f>
         <v>45845</v>
       </c>
-      <c r="BQ6" s="115"/>
-      <c r="BR6" s="115"/>
-      <c r="BS6" s="115"/>
-      <c r="BT6" s="115"/>
-      <c r="BU6" s="115">
+      <c r="BQ6" s="114"/>
+      <c r="BR6" s="114"/>
+      <c r="BS6" s="114"/>
+      <c r="BT6" s="114"/>
+      <c r="BU6" s="114">
         <f>BP6+7</f>
         <v>45852</v>
       </c>
-      <c r="BV6" s="115"/>
-      <c r="BW6" s="115"/>
-      <c r="BX6" s="115"/>
-      <c r="BY6" s="115"/>
-      <c r="BZ6" s="115">
+      <c r="BV6" s="114"/>
+      <c r="BW6" s="114"/>
+      <c r="BX6" s="114"/>
+      <c r="BY6" s="114"/>
+      <c r="BZ6" s="114">
         <f>BU6+7</f>
         <v>45859</v>
       </c>
-      <c r="CA6" s="115"/>
-      <c r="CB6" s="115"/>
-      <c r="CC6" s="115"/>
-      <c r="CD6" s="115"/>
-      <c r="CE6" s="115">
+      <c r="CA6" s="114"/>
+      <c r="CB6" s="114"/>
+      <c r="CC6" s="114"/>
+      <c r="CD6" s="114"/>
+      <c r="CE6" s="114">
         <f>BZ6+7</f>
         <v>45866</v>
       </c>
-      <c r="CF6" s="115"/>
-      <c r="CG6" s="115"/>
-      <c r="CH6" s="115"/>
-      <c r="CI6" s="115"/>
-      <c r="CJ6" s="115">
+      <c r="CF6" s="114"/>
+      <c r="CG6" s="114"/>
+      <c r="CH6" s="114"/>
+      <c r="CI6" s="114"/>
+      <c r="CJ6" s="114">
         <f>CE6+7</f>
         <v>45873</v>
       </c>
-      <c r="CK6" s="115"/>
-      <c r="CL6" s="115"/>
-      <c r="CM6" s="115"/>
-      <c r="CN6" s="115"/>
+      <c r="CK6" s="114"/>
+      <c r="CL6" s="114"/>
+      <c r="CM6" s="114"/>
+      <c r="CN6" s="114"/>
     </row>
     <row r="7" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="61"/>
@@ -9854,18 +9851,6 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="28">
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -9882,6 +9867,18 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G35">
@@ -9913,11 +9910,11 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="114">
+      <c r="E1" s="115">
         <v>46280</v>
       </c>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -10296,10 +10293,10 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -10394,148 +10391,148 @@
     </row>
     <row r="6" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="115">
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="114">
         <f>H7</f>
         <v>46279</v>
       </c>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="115">
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
+      <c r="M6" s="114">
         <f>H6+7</f>
         <v>46286</v>
       </c>
-      <c r="N6" s="115"/>
-      <c r="O6" s="115"/>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="115"/>
-      <c r="R6" s="115">
+      <c r="N6" s="114"/>
+      <c r="O6" s="114"/>
+      <c r="P6" s="114"/>
+      <c r="Q6" s="114"/>
+      <c r="R6" s="114">
         <f>M6+7</f>
         <v>46293</v>
       </c>
-      <c r="S6" s="115"/>
-      <c r="T6" s="115"/>
-      <c r="U6" s="115"/>
-      <c r="V6" s="115"/>
-      <c r="W6" s="115">
+      <c r="S6" s="114"/>
+      <c r="T6" s="114"/>
+      <c r="U6" s="114"/>
+      <c r="V6" s="114"/>
+      <c r="W6" s="114">
         <f>R6+7</f>
         <v>46300</v>
       </c>
-      <c r="X6" s="115"/>
-      <c r="Y6" s="115"/>
-      <c r="Z6" s="115"/>
-      <c r="AA6" s="115"/>
-      <c r="AB6" s="115">
+      <c r="X6" s="114"/>
+      <c r="Y6" s="114"/>
+      <c r="Z6" s="114"/>
+      <c r="AA6" s="114"/>
+      <c r="AB6" s="114">
         <f>W6+7</f>
         <v>46307</v>
       </c>
-      <c r="AC6" s="115"/>
-      <c r="AD6" s="115"/>
-      <c r="AE6" s="115"/>
-      <c r="AF6" s="115"/>
-      <c r="AG6" s="115">
+      <c r="AC6" s="114"/>
+      <c r="AD6" s="114"/>
+      <c r="AE6" s="114"/>
+      <c r="AF6" s="114"/>
+      <c r="AG6" s="114">
         <f>AB6+7</f>
         <v>46314</v>
       </c>
-      <c r="AH6" s="115"/>
-      <c r="AI6" s="115"/>
-      <c r="AJ6" s="115"/>
-      <c r="AK6" s="115"/>
-      <c r="AL6" s="115">
+      <c r="AH6" s="114"/>
+      <c r="AI6" s="114"/>
+      <c r="AJ6" s="114"/>
+      <c r="AK6" s="114"/>
+      <c r="AL6" s="114">
         <f>AG6+7</f>
         <v>46321</v>
       </c>
-      <c r="AM6" s="115"/>
-      <c r="AN6" s="115"/>
-      <c r="AO6" s="115"/>
-      <c r="AP6" s="115"/>
-      <c r="AQ6" s="115">
+      <c r="AM6" s="114"/>
+      <c r="AN6" s="114"/>
+      <c r="AO6" s="114"/>
+      <c r="AP6" s="114"/>
+      <c r="AQ6" s="114">
         <f>AL6+7</f>
         <v>46328</v>
       </c>
-      <c r="AR6" s="115"/>
-      <c r="AS6" s="115"/>
-      <c r="AT6" s="115"/>
-      <c r="AU6" s="115"/>
-      <c r="AV6" s="115">
+      <c r="AR6" s="114"/>
+      <c r="AS6" s="114"/>
+      <c r="AT6" s="114"/>
+      <c r="AU6" s="114"/>
+      <c r="AV6" s="114">
         <f>AQ6+7</f>
         <v>46335</v>
       </c>
-      <c r="AW6" s="115"/>
-      <c r="AX6" s="115"/>
-      <c r="AY6" s="115"/>
-      <c r="AZ6" s="115"/>
-      <c r="BA6" s="115">
+      <c r="AW6" s="114"/>
+      <c r="AX6" s="114"/>
+      <c r="AY6" s="114"/>
+      <c r="AZ6" s="114"/>
+      <c r="BA6" s="114">
         <f>AV6+7</f>
         <v>46342</v>
       </c>
-      <c r="BB6" s="115"/>
-      <c r="BC6" s="115"/>
-      <c r="BD6" s="115"/>
-      <c r="BE6" s="115"/>
-      <c r="BF6" s="115">
+      <c r="BB6" s="114"/>
+      <c r="BC6" s="114"/>
+      <c r="BD6" s="114"/>
+      <c r="BE6" s="114"/>
+      <c r="BF6" s="114">
         <f>BA6+7</f>
         <v>46349</v>
       </c>
-      <c r="BG6" s="115"/>
-      <c r="BH6" s="115"/>
-      <c r="BI6" s="115"/>
-      <c r="BJ6" s="115"/>
-      <c r="BK6" s="115">
+      <c r="BG6" s="114"/>
+      <c r="BH6" s="114"/>
+      <c r="BI6" s="114"/>
+      <c r="BJ6" s="114"/>
+      <c r="BK6" s="114">
         <f>BF6+7</f>
         <v>46356</v>
       </c>
-      <c r="BL6" s="115"/>
-      <c r="BM6" s="115"/>
-      <c r="BN6" s="115"/>
-      <c r="BO6" s="115"/>
-      <c r="BP6" s="115">
+      <c r="BL6" s="114"/>
+      <c r="BM6" s="114"/>
+      <c r="BN6" s="114"/>
+      <c r="BO6" s="114"/>
+      <c r="BP6" s="114">
         <f>BK6+7</f>
         <v>46363</v>
       </c>
-      <c r="BQ6" s="115"/>
-      <c r="BR6" s="115"/>
-      <c r="BS6" s="115"/>
-      <c r="BT6" s="115"/>
-      <c r="BU6" s="115">
+      <c r="BQ6" s="114"/>
+      <c r="BR6" s="114"/>
+      <c r="BS6" s="114"/>
+      <c r="BT6" s="114"/>
+      <c r="BU6" s="114">
         <f>BP6+7</f>
         <v>46370</v>
       </c>
-      <c r="BV6" s="115"/>
-      <c r="BW6" s="115"/>
-      <c r="BX6" s="115"/>
-      <c r="BY6" s="115"/>
-      <c r="BZ6" s="115">
+      <c r="BV6" s="114"/>
+      <c r="BW6" s="114"/>
+      <c r="BX6" s="114"/>
+      <c r="BY6" s="114"/>
+      <c r="BZ6" s="114">
         <f>BU6+7</f>
         <v>46377</v>
       </c>
-      <c r="CA6" s="115"/>
-      <c r="CB6" s="115"/>
-      <c r="CC6" s="115"/>
-      <c r="CD6" s="115"/>
-      <c r="CE6" s="115">
+      <c r="CA6" s="114"/>
+      <c r="CB6" s="114"/>
+      <c r="CC6" s="114"/>
+      <c r="CD6" s="114"/>
+      <c r="CE6" s="114">
         <f>BZ6+7</f>
         <v>46384</v>
       </c>
-      <c r="CF6" s="115"/>
-      <c r="CG6" s="115"/>
-      <c r="CH6" s="115"/>
-      <c r="CI6" s="115"/>
-      <c r="CJ6" s="115">
+      <c r="CF6" s="114"/>
+      <c r="CG6" s="114"/>
+      <c r="CH6" s="114"/>
+      <c r="CI6" s="114"/>
+      <c r="CJ6" s="114">
         <f>CE6+7</f>
         <v>46391</v>
       </c>
-      <c r="CK6" s="115"/>
-      <c r="CL6" s="115"/>
-      <c r="CM6" s="115"/>
-      <c r="CN6" s="115"/>
+      <c r="CK6" s="114"/>
+      <c r="CL6" s="114"/>
+      <c r="CM6" s="114"/>
+      <c r="CN6" s="114"/>
     </row>
     <row r="7" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A7" s="61"/>
@@ -12407,9 +12404,11 @@
         <v>46320</v>
       </c>
       <c r="F21" s="25">
-        <v>46318</v>
-      </c>
-      <c r="G21" s="25"/>
+        <v>46316</v>
+      </c>
+      <c r="G21" s="25">
+        <v>46316</v>
+      </c>
       <c r="H21" s="26"/>
       <c r="I21" s="27"/>
       <c r="J21" s="27"/>
@@ -13134,7 +13133,7 @@
         <v>46308</v>
       </c>
       <c r="E28" s="25">
-        <v>46317</v>
+        <v>46325</v>
       </c>
       <c r="F28" s="25">
         <v>46308</v>
@@ -13238,7 +13237,7 @@
         <v>46308</v>
       </c>
       <c r="E29" s="25">
-        <v>46317</v>
+        <v>46325</v>
       </c>
       <c r="F29" s="25">
         <v>46308</v>
@@ -13339,7 +13338,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="25">
-        <v>46321</v>
+        <v>46325</v>
       </c>
       <c r="E30" s="25">
         <v>46346</v>
@@ -13441,7 +13440,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="25">
-        <v>46321</v>
+        <v>46325</v>
       </c>
       <c r="E31" s="25">
         <v>46328</v>
@@ -15492,18 +15491,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -15520,9 +15507,21 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
-  <conditionalFormatting sqref="G43:G44 F9:G41">
+  <conditionalFormatting sqref="F9:G41 G43:G44">
     <cfRule type="expression" dxfId="0" priority="3">
       <formula>D9&lt;F9</formula>
     </cfRule>
@@ -15533,6 +15532,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A6A6C361903FA540AF4D79E6EA2B777C" ma:contentTypeVersion="18" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ea7c12cc56e366ff4dda5c6e96eadaab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaa52e1c-8772-4366-aa63-bf636c80ebd4" xmlns:ns3="0c73c1f5-50cd-4477-a315-44bef7b8a847" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7966d967ae6f075ad6e4da9e3740ee6a" ns2:_="" ns3:_="">
     <xsd:import namespace="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
@@ -15787,34 +15813,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8D2A65F-21CC-403E-82EF-9B2DA85938F8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15831,23 +15849,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/資料/ガントチャート_4GA3_遠藤直樹.xlsx
+++ b/資料/ガントチャート_4GA3_遠藤直樹.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B04CC0-DB5C-422E-89B9-F64331669267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527DE0C8-7778-421D-87B8-952A0FF2C396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24315" yWindow="2670" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4530" yWindow="1230" windowWidth="21600" windowHeight="12735" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="制作進捗確認表" sheetId="16" state="hidden" r:id="rId1"/>
@@ -1861,6 +1861,15 @@
     <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1883,15 +1892,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="182" fontId="1" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2484,22 +2484,22 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="115">
+      <c r="E1" s="118">
         <v>45761</v>
       </c>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
     </row>
     <row r="2" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -2507,15 +2507,15 @@
       <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -2523,15 +2523,15 @@
       <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -2539,10 +2539,10 @@
       <c r="L4" s="83"/>
     </row>
     <row r="5" spans="1:92" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
       <c r="AU5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2555,12 +2555,12 @@
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="119"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="122"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="125"/>
       <c r="H6" s="114">
         <f>H7</f>
         <v>45761</v>
@@ -2702,14 +2702,14 @@
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="123" t="s">
+      <c r="D7" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="124"/>
-      <c r="F7" s="125" t="s">
+      <c r="E7" s="116"/>
+      <c r="F7" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="124"/>
+      <c r="G7" s="116"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>45761</v>
@@ -6033,18 +6033,6 @@
   </sheetData>
   <sheetProtection password="DF87" sheet="1" insertRows="0"/>
   <mergeCells count="28">
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="AG6:AK6"/>
-    <mergeCell ref="AL6:AP6"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
     <mergeCell ref="BU6:BY6"/>
     <mergeCell ref="BZ6:CD6"/>
     <mergeCell ref="CE6:CI6"/>
@@ -6061,6 +6049,18 @@
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB6:AF6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="AG6:AK6"/>
+    <mergeCell ref="AL6:AP6"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G34">
@@ -6129,22 +6129,22 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="115">
+      <c r="E1" s="118">
         <v>45761</v>
       </c>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
     </row>
     <row r="2" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -6152,15 +6152,15 @@
       <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -6168,15 +6168,15 @@
       <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -6184,10 +6184,10 @@
       <c r="L4" s="83"/>
     </row>
     <row r="5" spans="1:92" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
       <c r="AU5" s="1" t="s">
         <v>5</v>
       </c>
@@ -6200,12 +6200,12 @@
     </row>
     <row r="6" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="119"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="122"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="125"/>
       <c r="H6" s="114">
         <f>H7</f>
         <v>45761</v>
@@ -6347,14 +6347,14 @@
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="123" t="s">
+      <c r="D7" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="124"/>
-      <c r="F7" s="125" t="s">
+      <c r="E7" s="116"/>
+      <c r="F7" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="124"/>
+      <c r="G7" s="116"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>45761</v>
@@ -9851,6 +9851,18 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="28">
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -9867,18 +9879,6 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G35">
@@ -9910,11 +9910,11 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="115">
+      <c r="E1" s="118">
         <v>46280</v>
       </c>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -10002,15 +10002,15 @@
       <c r="CN1" s="1"/>
     </row>
     <row r="2" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="119" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -10098,15 +10098,15 @@
       <c r="CN2" s="1"/>
     </row>
     <row r="3" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -10194,15 +10194,15 @@
       <c r="CN3" s="1"/>
     </row>
     <row r="4" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -10293,10 +10293,10 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -10391,12 +10391,12 @@
     </row>
     <row r="6" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="119"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="122"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="125"/>
       <c r="H6" s="114">
         <f>H7</f>
         <v>46279</v>
@@ -10538,14 +10538,14 @@
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="123" t="s">
+      <c r="D7" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="124"/>
-      <c r="F7" s="125" t="s">
+      <c r="E7" s="116"/>
+      <c r="F7" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="124"/>
+      <c r="G7" s="116"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>46279</v>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="105">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D11" s="12">
         <v>46306</v>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="B21" s="23"/>
       <c r="C21" s="106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="25">
         <v>46318</v>
@@ -15491,6 +15491,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -15507,18 +15519,6 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G41 G43:G44">
@@ -15532,33 +15532,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A6A6C361903FA540AF4D79E6EA2B777C" ma:contentTypeVersion="18" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ea7c12cc56e366ff4dda5c6e96eadaab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaa52e1c-8772-4366-aa63-bf636c80ebd4" xmlns:ns3="0c73c1f5-50cd-4477-a315-44bef7b8a847" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7966d967ae6f075ad6e4da9e3740ee6a" ns2:_="" ns3:_="">
     <xsd:import namespace="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
@@ -15813,26 +15786,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8D2A65F-21CC-403E-82EF-9B2DA85938F8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15849,4 +15830,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/資料/ガントチャート_4GA3_遠藤直樹.xlsx
+++ b/資料/ガントチャート_4GA3_遠藤直樹.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527DE0C8-7778-421D-87B8-952A0FF2C396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C94238-F6C5-4AD3-B7D0-DAF41A9E9712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4530" yWindow="1230" windowWidth="21600" windowHeight="12735" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1861,15 +1861,6 @@
     <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1892,6 +1883,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="182" fontId="1" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2484,22 +2484,22 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="118">
+      <c r="E1" s="115">
         <v>45761</v>
       </c>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
     </row>
     <row r="2" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -2507,15 +2507,15 @@
       <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -2523,15 +2523,15 @@
       <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A4" s="119" t="s">
+      <c r="A4" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -2539,10 +2539,10 @@
       <c r="L4" s="83"/>
     </row>
     <row r="5" spans="1:92" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
       <c r="AU5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2555,12 +2555,12 @@
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="123"/>
-      <c r="F6" s="124"/>
-      <c r="G6" s="125"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="122"/>
       <c r="H6" s="114">
         <f>H7</f>
         <v>45761</v>
@@ -2702,14 +2702,14 @@
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="115" t="s">
+      <c r="D7" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="116"/>
-      <c r="F7" s="117" t="s">
+      <c r="E7" s="124"/>
+      <c r="F7" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="116"/>
+      <c r="G7" s="124"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>45761</v>
@@ -6033,6 +6033,18 @@
   </sheetData>
   <sheetProtection password="DF87" sheet="1" insertRows="0"/>
   <mergeCells count="28">
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="AG6:AK6"/>
+    <mergeCell ref="AL6:AP6"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="BU6:BY6"/>
     <mergeCell ref="BZ6:CD6"/>
     <mergeCell ref="CE6:CI6"/>
@@ -6049,18 +6061,6 @@
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB6:AF6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="AG6:AK6"/>
-    <mergeCell ref="AL6:AP6"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G34">
@@ -6129,22 +6129,22 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="118">
+      <c r="E1" s="115">
         <v>45761</v>
       </c>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
     </row>
     <row r="2" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -6152,15 +6152,15 @@
       <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -6168,15 +6168,15 @@
       <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="119" t="s">
+      <c r="A4" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -6184,10 +6184,10 @@
       <c r="L4" s="83"/>
     </row>
     <row r="5" spans="1:92" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
       <c r="AU5" s="1" t="s">
         <v>5</v>
       </c>
@@ -6200,12 +6200,12 @@
     </row>
     <row r="6" spans="1:92" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="123"/>
-      <c r="F6" s="124"/>
-      <c r="G6" s="125"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="122"/>
       <c r="H6" s="114">
         <f>H7</f>
         <v>45761</v>
@@ -6347,14 +6347,14 @@
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="115" t="s">
+      <c r="D7" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="116"/>
-      <c r="F7" s="117" t="s">
+      <c r="E7" s="124"/>
+      <c r="F7" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="116"/>
+      <c r="G7" s="124"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>45761</v>
@@ -9851,18 +9851,6 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="28">
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -9879,6 +9867,18 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G35">
@@ -9910,11 +9910,11 @@
       <c r="D1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="118">
+      <c r="E1" s="115">
         <v>46280</v>
       </c>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -10002,15 +10002,15 @@
       <c r="CN1" s="1"/>
     </row>
     <row r="2" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="116" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
       <c r="J2" s="83"/>
@@ -10098,15 +10098,15 @@
       <c r="CN2" s="1"/>
     </row>
     <row r="3" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
       <c r="J3" s="83"/>
@@ -10194,15 +10194,15 @@
       <c r="CN3" s="1"/>
     </row>
     <row r="4" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
-      <c r="A4" s="119" t="s">
+      <c r="A4" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
       <c r="J4" s="83"/>
@@ -10293,10 +10293,10 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -10391,12 +10391,12 @@
     </row>
     <row r="6" spans="1:92" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="123"/>
-      <c r="F6" s="124"/>
-      <c r="G6" s="125"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="122"/>
       <c r="H6" s="114">
         <f>H7</f>
         <v>46279</v>
@@ -10538,14 +10538,14 @@
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="115" t="s">
+      <c r="D7" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="116"/>
-      <c r="F7" s="117" t="s">
+      <c r="E7" s="124"/>
+      <c r="F7" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="116"/>
+      <c r="G7" s="124"/>
       <c r="H7" s="63">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>46279</v>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="105">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D11" s="12">
         <v>46306</v>
@@ -11384,7 +11384,9 @@
       <c r="F11" s="12">
         <v>46306</v>
       </c>
-      <c r="G11" s="12"/>
+      <c r="G11" s="12">
+        <v>46318</v>
+      </c>
       <c r="H11" s="13"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
@@ -14426,7 +14428,9 @@
       <c r="F41" s="72">
         <v>46280</v>
       </c>
-      <c r="G41" s="72"/>
+      <c r="G41" s="72">
+        <v>46290</v>
+      </c>
       <c r="H41" s="73"/>
       <c r="I41" s="74"/>
       <c r="J41" s="74"/>
@@ -15491,18 +15495,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -15519,6 +15511,18 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F9:G41 G43:G44">
@@ -15532,6 +15536,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A6A6C361903FA540AF4D79E6EA2B777C" ma:contentTypeVersion="18" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ea7c12cc56e366ff4dda5c6e96eadaab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaa52e1c-8772-4366-aa63-bf636c80ebd4" xmlns:ns3="0c73c1f5-50cd-4477-a315-44bef7b8a847" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7966d967ae6f075ad6e4da9e3740ee6a" ns2:_="" ns3:_="">
     <xsd:import namespace="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
@@ -15786,34 +15817,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8D2A65F-21CC-403E-82EF-9B2DA85938F8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15830,23 +15853,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>